--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,7 +559,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Input JSON</t>
+          <t>Input JSON (what we sent)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -568,19 +569,24 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Output / Error</t>
+          <t>Output / Error (what we got back)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>D2.1-1</t>
+          <t>D2.2-2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -590,98 +596,10 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2.1-04_no_prefix_section</t>
+          <t>2.2-04_native_string</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>{
-  "entity": {
-    "prov:e1": {}
-  }
-}</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>The "prefix" section is optional per the PROV-JSON spec. When a valid document omits it, ProvToolbox crashes with a NullPointerException instead of accepting the input. Any PROV-JSON file without a prefix section cannot be read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>D2.1-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2.1-07_blank_node_entity</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>{
-  "prefix": {
-    "ex": "http://example.org/"
-  },
-  "entity": {
-    "_:e1": {},
-    "ex:e2": {}
-  }
-}</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Blank nodes (anonymous identifiers starting with "_:") are valid in the PROV-JSON spec. When an entity, agent, or activity uses a blank node ID, ProvToolbox crashes during serialization. The data is read in successfully, but writing it back out fails.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>D2.2-2</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2.2-04_native_string</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -696,40 +614,46 @@
 }</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>The PROV-JSON spec allows native JSON values (plain strings, numbers, booleans) as attribute values. When a native value is the sole attribute value, ProvToolbox silently drops it. No error is raised — the data simply disappears from the output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Spec §2.2 says native JSON values (strings, numbers, booleans) "MAY be represented using the JSON native data types." This is an explicit MAY — native values are valid input.
+When a native value is the sole attribute value, ProvToolbox silently drops it. No error is raised — the data simply disappears from the output.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Spec §2.2, "MAY" keyword</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>D2.2-3</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>2.2-03_spec_example3_mixed_array</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -748,40 +672,46 @@
 }</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>The spec allows arrays containing a mix of typed values ({"$":..., "type":...}) and native JSON values (plain numbers, booleans). ProvToolbox crashes when attempting to serialize such an array. This test uses Example 3 from the spec itself.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Spec §2.2 Example 3 explicitly shows an array mixing typed values ({"$":"1034","type":"xsd:positiveInteger"}) with a plain integer (2). This is the spec's own example.
+ProvToolbox crashes when attempting to serialize this array.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Spec §2.2, Example 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>D2.2-5</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>2.2-15_prov_value_typed</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -796,40 +726,46 @@
 }</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>The prov:value attribute is defined in the PROV data model to hold the actual value content of an entity. ProvToolbox reads it in but fails to write it back out — the value content is lost. This affects any entity or agent that carries a prov:value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>prov:value is a defined PROV-DM attribute for holding the actual value content of an entity. ProvToolbox reads it in but fails to write it back out — the value content is lost.
+This affects any entity or agent that carries a prov:value attribute.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>PROV-DM attribute definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>D2.2-6</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>2.2-21_json_null_value</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -844,88 +780,46 @@
 }</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>When an attribute value is JSON null, ProvToolbox crashes with a NullPointerException. While null is not a defined PROV-JSON value type, the parser should reject it gracefully rather than crash. This test expects PARSE_FAILED — ProvToolbox does fail, but via an unhandled crash rather than a clean error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>D3.1.3-1</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>When an attribute value is JSON null, ProvToolbox crashes with a NullPointerException. Null is not a defined PROV-JSON value type, so rejection is correct — but the failure should be a clean parse error, not an unhandled crash.
+This test expects a parse failure. ProvToolbox does fail, but via crash.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Not a valid PROV-JSON value type</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>D3.3-1</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>3.1.3-03_start_time_only</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>{
-  "prefix": {
-    "ex": "http://example.org/"
-  },
-  "activity": {
-    "ex:a1": {
-      "prov:startTime": "2011-11-16T16:05:00",
-      "prov:type": {"$": "ex:Computation", "type": "prov:QualifiedName"}
-    }
-  }
-}</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Timestamps are silently modified during round-trip. A time like "2023-01-15T10:30:00" is rewritten as "2023-01-15T10:30:00.000+00:00" — milliseconds and timezone offset are injected. Sub-millisecond precision is truncated. The original format is not preserved. This affects all activities with start or end times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>D3.3-1</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>3.3-01_minimal_bundle</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>{
   "prefix": { "ex": "http://example.org/" },
@@ -939,257 +833,116 @@
 }</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Bundles are a core PROV-JSON feature for grouping provenance statements (spec Section 3.3). Every bundle test crashes with a NullPointerException. The deserialiser fails to set the bundle ID before processing its contents. No bundle can be read from PROV-JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Bundles are containers for grouping provenance statements (Spec §3.3). The spec defines them with multiple examples (Examples 40-41).
+Every single bundle test crashes with a NullPointerException. No bundle can be read from PROV-JSON. This blocks a core use case of the format.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Spec §3.3, Examples 40-41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CRITICAL ISSUES — COMMON PATTERNS</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in §2.2). ProvToolbox either drops them silently (D2.2-2) or crashes when they appear in mixed arrays (D2.2-3). Combined with prov:value being lost (D2.2-5), any provenance document using the simpler value formats will lose data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Bundles completely non-functional: Every single bundle test crashes (D3.3-1). Bundles are the primary mechanism for grouping and attributing provenance — this blocks a core use case of PROV-JSON.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Crash on valid optional features: 3 of 8 critical issues are crashes caused by valid but optional parts of the spec — missing prefix section (D2.1-1), blank node identifiers (D2.1-2), and bundles (D3.3-1). ProvToolbox assumes these features are either always present or never used, and throws NullPointerExceptions when that assumption is wrong.</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>HIGH ISSUES</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Silent data loss on native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values. ProvToolbox either drops them silently (D2.2-2) or crashes when they appear in mixed arrays (D2.2-3). Combined with prov:value being lost (D2.2-5), any provenance document using the simpler value formats will lose data.</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON (what we sent)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error (what we got back)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Timestamp modification: All timestamps are silently normalised — milliseconds added, timezone injected, sub-millisecond precision truncated (D3.1.3-1). This means ProvToolbox changes the actual content of time values rather than preserving them as written.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Bundles completely non-functional: Every single bundle test crashes (D3.3-1). Since bundles are the primary mechanism for grouping and attributing provenance, this blocks a core use case of PROV-JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>HIGH ISSUES</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>D2.1-3</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>D2.1-7</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>2.1-08_same_iri_two_qnames</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>{
-  "prefix": {
-    "ex": "http://example.org/",
-    "other": "http://example.org/"
-  },
-  "entity": {
-    "ex:foo": {},
-    "other:foo": {}
-  }
-}</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>When two different prefix names map to the same IRI (e.g., "ex1:" and "ex2:" both pointing to "http://example.org/"), ProvToolbox merges them into one. The distinction between the two qualified names is lost. Entities that had different prefixes come out with the same one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>D2.1-4</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>2.1-09_full_uri_identifier</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>{
-  "prefix": {
-    "ex": "http://example.org/"
-  },
-  "entity": {
-    "http://example.org/entity1": {}
-  }
-}</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>The PROV-JSON spec allows full URIs as identifiers (e.g., "http://example.org/entity1"). ProvToolbox only accepts prefixed qualified names (e.g., "ex:entity1"). When a full URI is used, parsing fails. This means any PROV-JSON using full IRIs instead of QNames cannot be processed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>D2.1-6</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>2.1-11_null_prefix_value</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>{
-  "prefix": {
-    "ex": "http://example.org/",
-    "bad": null
-  },
-  "entity": {
-    "ex:e1": {}
-  }
-}</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>When a prefix maps to a JSON null value instead of a string IRI, ProvToolbox crashes with a NullPointerException. While null is not a valid namespace IRI and rejection is acceptable, the crash is unhandled. This test expects PARSE_FAILED — the issue is that the failure is via an uncontrolled crash.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>D2.1-7</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>2.1-12_user_underscore_prefix</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1202,40 +955,46 @@
 }</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>ProvToolbox internally reserves the "_" prefix for blank nodes. If a user's PROV-JSON data defines "_" as a regular namespace prefix (e.g., "_": "http://example.org/"), ProvToolbox silently overwrites it with its own blank node mapping. The user's namespace is lost without any warning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>ProvToolbox internally reserves the "_" prefix for blank nodes. If a user's data defines "_" as a regular namespace prefix (e.g., "_": "http://example.org/"), ProvToolbox silently overwrites it with its own blank node mapping.
+The user's namespace is lost without any warning.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Spec §2.1, blank node identifiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>D2.2-1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>2.2-01_spec_example1_typed</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1252,40 +1011,46 @@
 }</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>The PROV-JSON spec defines typed values as JSON objects: {"$": "value", "type": "xsd:int"}. ProvToolbox outputs them as 2-element arrays: ["value", "xsd:int"]. This is a different format that other spec-compliant tools will not recognise. Affects all typed attribute values across all element types.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Spec §2.2 defines typed values as JSON objects: {"$": "value", "type": "xsd:int"}. ProvToolbox outputs them as 2-element arrays: ["value", "xsd:int"].
+This is not a cosmetic difference — any other spec-compliant tool reading ProvToolbox output will fail to parse the typed values. Affects all typed attribute values.</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Spec §2.2, Example 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>D2.2-7</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>2.2-19_native_string_array</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1300,40 +1065,46 @@
 }</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Native JSON strings are handled inconsistently. A single native string as an attribute value is silently dropped (see D2.2-2), but native strings inside an array are preserved. The same data type behaves differently depending on whether it appears alone or in a list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Native JSON strings are handled inconsistently. A single native string as an attribute value is silently dropped (see D2.2-2), but native strings inside an array are preserved.
+The same data type behaves differently depending on whether it appears alone or in a list.</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Spec §2.2, MAY keyword</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>D2.2-8</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>2.2-27_typed_xsd_string_vs_native</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1348,40 +1119,46 @@
 }</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>The 2-element array format ProvToolbox uses for typed values (see D2.2-1) has an additional problem: the order of elements within the array is not deterministic. It depends on Java hash codes, so the value and type may appear in either position. This makes the output unpredictable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>The 2-element array format ProvToolbox uses (see D2.2-1) has an additional problem: the order of elements within the array is not deterministic. It depends on Java hash codes, so the value and type may appear in either position.
+This makes the already-incorrect output additionally unpredictable.</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Consequence of D2.2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>3.1.2-06_agent_prov_value</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1395,40 +1172,46 @@
 }</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>When an agent has a prov:value attribute, ProvToolbox drops it entirely during serialization. The value is read in but does not appear in the output. This is complete data loss for any agent that carries a prov:value attribute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>When an agent has a prov:value attribute, ProvToolbox drops it entirely during serialization. The value is read in but does not appear in the output.
+This is complete data loss for any agent that carries a prov:value attribute.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>PROV-DM attribute definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-2</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>3.1.2-10_agent_multivalue_attr</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1445,40 +1228,99 @@
 }</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>When an agent has an attribute with multiple xsd:string typed values, the type annotation is stripped from the output. The values survive but lose their type information, changing their meaning.</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Spec §2.2, typed values</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>D3.1.3-1</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>3.1.3-03_start_time_only</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>{
+  "prefix": {
+    "ex": "http://example.org/"
+  },
+  "activity": {
+    "ex:a1": {
+      "prov:startTime": "2011-11-16T16:05:00",
+      "prov:type": {"$": "ex:Computation", "type": "prov:QualifiedName"}
+    }
+  }
+}</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Error: Could not find or load main class JsonRoundTrip
+Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Timestamps are silently modified during round-trip. A time like "2023-01-15T10:30:00" is rewritten as "2023-01-15T10:30:00.000+00:00".
+The spec says timestamps MUST conform to xsd:dateTime but does not explicitly require preserving the exact lexical form. However, injecting "+00:00" changes the meaning — timezone-unspecified becomes explicitly UTC. Spec Example 9 shows timestamps without timezone or milliseconds.</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Spec §3.1.3, Example 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>D-DICT-1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>B.1-01_spec_example46</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>{
     "prefix": {
@@ -1509,164 +1351,130 @@
 }</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>The PROV-JSON spec includes dictionary extensions (Appendix B): hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom. ProvToolbox does not recognise any of these in JSON format. The dictionary-related data is silently discarded during round-trip. All three dictionary operation types are affected.</t>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>The spec defines dictionary extensions in Appendix B: hadDictionaryMember (B.1), derivedByInsertionFrom (B.2), derivedByRemovalFrom (B.3), with Examples 46-52.
+ProvToolbox does not recognise any of these in JSON format. All dictionary data is silently discarded during round-trip.</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Spec Appendix B, Examples 46-52</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HIGH ISSUES — COMMON PATTERNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays instead of the spec-defined object format with "$" and "type" properties (D2.2-1). Any other spec-compliant tool reading ProvToolbox output will not recognise the typed values. Combined with non-deterministic element order (D2.2-8), the output is both incorrect and unpredictable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Inconsistent attribute handling: Native string values behave differently depending on context — dropped when alone, kept when in an array (D2.2-7). Agent-specific attributes like prov:value are dropped entirely (D3.1.2-1), and multi-value type annotations are stripped (D3.1.2-2). These inconsistencies make it difficult to predict which data will survive a round-trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Timestamps semantically altered: All timestamps have timezone and milliseconds injected (D3.1.3-1). While the spec does not explicitly require exact lexical preservation, adding "+00:00" changes a timezone-unspecified time to explicitly UTC — a semantic change, not just a formatting one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Dictionary extensions completely absent: All three PROV-Dictionary operations from Appendix B are unrecognised (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>MEDIUM ISSUES</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>HIGH ISSUES — COMMON PATTERNS</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON (what we sent)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error (what we got back)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays instead of the spec-defined object format (D2.2-1). This is not a cosmetic difference — any other spec-compliant tool reading ProvToolbox output will fail to parse the typed values. Combined with non-deterministic element order (D2.2-8), the output is both wrong and unpredictable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Identifier handling gaps: Full URIs are rejected (D2.1-4), same-IRI prefixes are merged (D2.1-3), and the underscore prefix is silently overwritten (D2.1-7). These restrict how identifiers can be expressed in PROV-JSON and can cause data loss when exchanging documents between systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Inconsistent attribute handling: Native string values behave differently depending on context — dropped when alone, kept when in an array (D2.2-7). Agent-specific attributes like prov:value are dropped entirely (D3.1.2-1), and multi-value type annotations are stripped (D3.1.2-2). These inconsistencies make it difficult to predict which data will survive a round-trip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Dictionary extensions not supported: All three PROV-Dictionary operations from Appendix B are unrecognised (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>D2.1-5</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>D2.2-4</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>2.1-10_default_as_prefix_name</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>{
-  "prefix": {
-    "default": "http://example.org/default/"
-  },
-  "entity": {
-    "default:foo": {}
-  }
-}</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>The word "default" cannot be used as a prefix name even though it is a valid JSON key. ProvToolbox treats "default" as a reserved word internally, causing incorrect qualified name resolution. The prefix mapping is not preserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>D2.2-4</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1685,40 +1493,46 @@
 }</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>When an attribute has multiple values in an array, the order of values may change in the output. ProvToolbox stores attributes in a HashSet (unordered) rather than preserving insertion order. While the values survive, their sequence is not guaranteed to match the input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>When an attribute has multiple values in an array, the order of values may change in the output. Array order is semantically significant in JSON.
+The spec says values MUST be collated into a JSON array but does not explicitly require preserving order.</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Spec §2.2, array collation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>D3.1.1-4</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>3.1.1-03_multiple_entities</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1734,105 +1548,109 @@
 }</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>The order of elements within sections (e.g., the order of entities within the "entity" object) is not preserved. ProvToolbox stores elements in a HashMap, so they may come out in a different order than the input. The data is intact but the structure changes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>The order of elements within sections (e.g., the order of entities within the "entity" object) is not preserved. JSON object key order is not guaranteed by the JSON specification, but many systems depend on it in practice.
+The data is intact but the structure changes.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>JSON RFC 8259, unordered objects</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>MEDIUM ISSUES — COMMON PATTERNS</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Ordering not preserved: Both element order within sections (D3.1.1-4) and value order within multi-value attributes (D2.2-4) may change. ProvToolbox uses hash-based collections internally, so insertion order is lost. While JSON object key order is technically unspecified, many systems depend on it in practice, and array order is semantically significant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Reserved word conflict: The prefix name "default" cannot be used because ProvToolbox treats it as a reserved word internally (D2.1-5). This is a minor interoperability issue — documents using "default" as a prefix name will not round-trip correctly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Ordering not preserved: Both value order within multi-value attributes (D2.2-4) and element order within sections (D3.1.1-4) may change. While JSON object key order is not guaranteed by the JSON specification, array order is semantically significant. These changes may cause issues with systems that depend on consistent ordering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>LOW ISSUES</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Issue ID</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON (what we sent)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error (what we got back)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Problem Description</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-5</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>3.1.1-08_duplicate_entity_id</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1851,40 +1669,45 @@
 }</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>When the input JSON contains duplicate keys (same entity ID appearing twice), only the last occurrence is kept. This is standard JSON parser behaviour and not specific to ProvToolbox, but it means data under the earlier key is silently lost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>When the input JSON contains duplicate keys (same entity ID appearing twice), only the last occurrence is kept. This is standard JSON parser behaviour per RFC 8259 and not specific to ProvToolbox.</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>RFC 8259</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-7</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>3.1.1-20_prov_role</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1898,40 +1721,45 @@
 }</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>The prov:role attribute is silently dropped when used on elements (entities, agents, activities). The spec allows prov:role on any element, but ProvToolbox only preserves it on relations. No error is raised — the attribute simply does not appear in the output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>prov:role is silently dropped when used on elements (entities, agents, activities). PROV-DM defines prov:role for relations, not elements — but elements can have arbitrary additional attributes, so prov:role should still be preserved as a generic attribute.</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>PROV-DM attribute scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-8</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>3.1.1-12_empty_entity_section</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1941,40 +1769,45 @@
 }</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>Empty statement sections (e.g., "entity": {}) are dropped from the output. The spec allows empty sections as valid JSON, but ProvToolbox omits them. The provenance data is unaffected since no statements are lost, but the document structure changes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>Empty statement sections (e.g., "entity": {}) are dropped from the output. The spec does not explicitly require preserving empty sections. No provenance data is lost.</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Not addressed in spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>D3.2.2-1</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>3.2.2-02_named_minimal</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>{
   "prefix": {
@@ -1989,58 +1822,60 @@
 }</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Error: Could not find or load main class JsonRoundTrip
 Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>The order of properties within relation objects (e.g., "prov:entity" before "prov:activity" vs the reverse) is changed in the output. ProvToolbox uses its own property ordering rather than preserving the input order. Data is intact but JSON structure differs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>The order of properties within relation objects (e.g., "prov:entity" before "prov:activity" vs the reverse) is changed in the output. JSON object key order is not guaranteed. Data is intact but JSON structure differs.</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>JSON RFC 8259, unordered objects</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>LOW ISSUES — COMMON PATTERNS</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Minor structural differences: These issues involve cosmetic changes to the JSON output — property ordering, empty section omission, duplicate key handling, and dropped prov:role on elements. No provenance data is lost in any of these cases. They may cause issues with strict byte-for-byte comparison tools but do not affect the semantic content of the provenance.</t>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Minor structural differences: These involve cosmetic changes to the JSON output — property ordering, empty section omission, duplicate key handling, and prov:role scope. No provenance data is lost. They may cause issues with strict byte-for-byte comparison but do not affect semantic content.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A47:G47"/>
+  <mergeCells count="16">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,28 +26,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -56,52 +55,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C0392B"/>
+        <fgColor rgb="002F4F4F"/>
+        <bgColor rgb="002F4F4F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5D8DC"/>
+        <fgColor rgb="00FFCDD2"/>
+        <bgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
+        <fgColor rgb="00FFE0B2"/>
+        <bgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E67E22"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDEBD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F39C12"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF9E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007F8C8D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F3F4"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,45 +94,54 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D5D8DC"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00D5D8DC"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00D5D8DC"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D5D8DC"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -525,13 +513,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,9 +587,9 @@
           <t>2.2-04_native_string</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
@@ -611,29 +599,36 @@
       "ex:name": "hello"
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"default" : "http://example.org/",
+"ex" : "http://example.org/"
+},
+"entity" : {
+"e1" : { }
+}
 }</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Spec §2.2 says native JSON values (strings, numbers, booleans) "MAY be represented using the JSON native data types." This is an explicit MAY — native values are valid input.
-When a native value is the sole attribute value, ProvToolbox silently drops it. No error is raised — the data simply disappears from the output.</t>
+          <t>Native JSON values silently dropped as sole attribute values. The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox drops them silently — the attribute disappears from the output.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Spec §2.2, "MAY" keyword</t>
+          <t>Spec Section 2.2, "MAY" keyword</t>
         </is>
       </c>
     </row>
@@ -653,9 +648,9 @@
           <t>2.2-03_spec_example3_mixed_array</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
@@ -669,29 +664,28 @@
       ]
     }
   }
-}</t>
+}
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
+          <t>SERIALIZE_FAILED</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>EXCEPTION: UncheckedException: Unchecked Exception</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Spec §2.2 Example 3 explicitly shows an array mixing typed values ({"$":"1034","type":"xsd:positiveInteger"}) with a plain integer (2). This is the spec's own example.
-ProvToolbox crashes when attempting to serialize this array.</t>
+          <t>Native number/boolean in mixed arrays crash the serialiser. Spec Section 2.2 Example 3 explicitly shows an array mixing typed values and a plain integer 2. ProvToolbox parses this OK but crashes with UncheckedException when serialising back.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Spec §2.2, Example 3</t>
+          <t>Spec Section 2.2, Example 3</t>
         </is>
       </c>
     </row>
@@ -711,9 +705,9 @@
           <t>2.2-15_prov_value_typed</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
@@ -723,24 +717,33 @@
       "prov:value": {"$": "42", "type": "xsd:int"}
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"default" : "http://example.org/",
+"ex" : "http://example.org/"
+},
+"entity" : {
+"e1" : {
+"prov:value" : [ "xsd:int" ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>prov:value is a defined PROV-DM attribute for holding the actual value content of an entity. ProvToolbox reads it in but fails to write it back out — the value content is lost.
-This affects any entity or agent that carries a prov:value attribute.</t>
+          <t>prov:value loses its data content on round-trip. prov:value is a defined PROV-DM attribute for holding the actual content/value of an entity. The data is read in successfully but not written back out.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -765,9 +768,9 @@
           <t>2.2-21_json_null_value</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
@@ -777,29 +780,30 @@
       "ex:missing": null
     }
   }
-}</t>
+}
+</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
+          <t>PARSE_FAILED</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>EXCEPTION: UncheckedException: Unchecked Exception
+CAUSED_BY: JsonMappingException: Cannot invoke "java.util.Collection.iterator()" because "attributes" is null (through reference chain: org.openprovenance.prov.core.json.serialization.SortedDocument["entity"]-&gt;java.util.LinkedHashMap["e1"]-&gt;org.openprovenance.prov.vanilla.Entity["ex:missing"])
+CAUSED_BY: NullPointerException: Cannot invoke "java.util.Collection.iterator()" because "attributes" is null</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>When an attribute value is JSON null, ProvToolbox crashes with a NullPointerException. Null is not a defined PROV-JSON value type, so rejection is correct — but the failure should be a clean parse error, not an unhandled crash.
-This test expects a parse failure. ProvToolbox does fail, but via crash.</t>
+          <t>JSON null as attribute value crashes the parser with an unhandled NullPointerException. While null is not a defined PROV-JSON value type, the parser should reject it with a clean error message, not an unhandled crash.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Not a valid PROV-JSON value type</t>
+          <t>Defensive error handling</t>
         </is>
       </c>
     </row>
@@ -819,9 +823,9 @@
           <t>3.3-01_minimal_bundle</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": { "ex": "http://example.org/" },
   "bundle": {
     "ex:bundle1": {
@@ -830,55 +834,56 @@
       }
     }
   }
-}</t>
+}
+</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
+          <t>PARSE_FAILED</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>EXCEPTION: UncheckedException: Unchecked Exception
+CAUSED_BY: JsonMappingException: Cannot invoke "org.openprovenance.prov.model.QualifiedName.getPrefix()" because "this.id" is null (through reference chain: org.openprovenance.prov.core.json.serialization.SortedDocument["bundle"]-&gt;java.util.HashMap["ex:bundle1"])
+CAUSED_BY: NullPointerException: Cannot invoke "org.openprovenance.prov.model.QualifiedName.getPrefix()" because "this.id" is null</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Bundles are containers for grouping provenance statements (Spec §3.3). The spec defines them with multiple examples (Examples 40-41).
-Every single bundle test crashes with a NullPointerException. No bundle can be read from PROV-JSON. This blocks a core use case of the format.</t>
+          <t>Bundle deserialisation completely broken. Every single bundle test crashes with NullPointerException. Bundles are the primary mechanism for grouping and attributing provenance (Section 3.3).</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Spec §3.3, Examples 40-41</t>
+          <t>Spec Section 3.3, Examples 40-41</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>CRITICAL ISSUES — COMMON PATTERNS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in §2.2). ProvToolbox either drops them silently (D2.2-2) or crashes when they appear in mixed arrays (D2.2-3). Combined with prov:value being lost (D2.2-5), any provenance document using the simpler value formats will lose data.</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox either drops them silently (D2.2-2) or crashes when they appear in mixed arrays (D2.2-3). Combined with prov:value being lost (D2.2-5), any provenance document using the simpler value formats will lose data.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Bundles completely non-functional: Every single bundle test crashes (D3.3-1). Bundles are the primary mechanism for grouping and attributing provenance — this blocks a core use case of PROV-JSON.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>HIGH ISSUES</t>
         </is>
@@ -942,9 +947,9 @@
           <t>2.1-12_user_underscore_prefix</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/",
     "_": "http://example.org/my-blanks/"
@@ -952,29 +957,35 @@
   "entity": {
     "ex:e1": {}
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"entity" : {
+"ex:e1" : { }
+}
 }</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>ProvToolbox internally reserves the "_" prefix for blank nodes. If a user's data defines "_" as a regular namespace prefix (e.g., "_": "http://example.org/"), ProvToolbox silently overwrites it with its own blank node mapping.
-The user's namespace is lost without any warning.</t>
+          <t>User-defined "_" prefix silently overridden by internal blank node mapping. The spec defines "_:" for blank node identifiers per Turtle nodeID production. A user-defined "_" namespace prefix is silently overwritten.</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Spec §2.1, blank node identifiers</t>
+          <t>Spec Section 2.1</t>
         </is>
       </c>
     </row>
@@ -994,9 +1005,9 @@
           <t>2.2-01_spec_example1_typed</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
@@ -1008,29 +1019,40 @@
       "ex:content": {"$": "Y29udGVudCBoZXJl", "type": "xsd:base64Binary"}
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"default" : "http://example.org/",
+"ex" : "http://example.org/"
+},
+"entity" : {
+"e1" : {
+"ex:byteSize" : [ "xsd:positiveInteger", "1034" ],
+"ex:content" : [ "xsd:base64Binary", "Y29udGVudCBoZXJl" ],
+"ex:compression" : [ "82.5e-2", "xsd:double" ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Spec §2.2 defines typed values as JSON objects: {"$": "value", "type": "xsd:int"}. ProvToolbox outputs them as 2-element arrays: ["value", "xsd:int"].
-This is not a cosmetic difference — any other spec-compliant tool reading ProvToolbox output will fail to parse the typed values. Affects all typed attribute values.</t>
+          <t>Typed values serialised as 2-element arrays instead of {"$":..., "type":...} objects. The spec defines typed values as JSON objects with "$" and "type" properties. ProvToolbox outputs [value, type] arrays instead.</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Spec §2.2, Example 1</t>
+          <t>Spec Section 2.2, "$" and "type" properties</t>
         </is>
       </c>
     </row>
@@ -1050,9 +1072,9 @@
           <t>2.2-19_native_string_array</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
@@ -1062,29 +1084,38 @@
       "ex:tags": ["alpha", "beta", "gamma"]
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"default" : "http://example.org/",
+"ex" : "http://example.org/"
+},
+"entity" : {
+"e1" : {
+"ex:tags" : [ "beta", "alpha", "gamma" ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Native JSON strings are handled inconsistently. A single native string as an attribute value is silently dropped (see D2.2-2), but native strings inside an array are preserved.
-The same data type behaves differently depending on whether it appears alone or in a list.</t>
+          <t>Native strings behave differently depending on context. When a native string is the sole attribute value, it is dropped (D2.2-2). When in an array, it survives. The spec allows native types equally in both contexts.</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Spec §2.2, MAY keyword</t>
+          <t>Spec Section 2.2</t>
         </is>
       </c>
     </row>
@@ -1101,44 +1132,66 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2.2-27_typed_xsd_string_vs_native</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>{
+          <t>2.2-10_array_typed_values</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
   },
   "entity": {
     "e1": {
-      "ex:name": {"$": "hello", "type": "xsd:string"}
+      "ex:scores": [
+        {"$": "95", "type": "xsd:int"},
+        {"$": "87", "type": "xsd:int"},
+        {"$": "72", "type": "xsd:int"}
+      ]
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"default" : "http://example.org/",
+"ex" : "http://example.org/"
+},
+"entity" : {
+"e1" : {
+"ex:scores" : [ {
+"type" : "xsd:int",
+"$" : "95"
+}, {
+"type" : "xsd:int",
+"$" : "87"
+}, {
+"type" : "xsd:int",
+"$" : "72"
+} ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>The 2-element array format ProvToolbox uses (see D2.2-1) has an additional problem: the order of elements within the array is not deterministic. It depends on Java hash codes, so the value and type may appear in either position.
-This makes the already-incorrect output additionally unpredictable.</t>
+          <t>2-element array output has non-deterministic element order. The [value, type] arrays from D2.2-1 have unpredictable element order depending on Java hash codes, making the already-incorrect format additionally unreliable.</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Consequence of D2.2-1</t>
+          <t>Spec Section 2.2</t>
         </is>
       </c>
     </row>
@@ -1158,9 +1211,9 @@
           <t>3.1.2-06_agent_prov_value</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
@@ -1169,24 +1222,30 @@
       "prov:value": {"$": "agent-data-123", "type": "xsd:string"}
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"agent" : {
+"ex:ag1" : { }
+}
 }</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>When an agent has a prov:value attribute, ProvToolbox drops it entirely during serialization. The value is read in but does not appear in the output.
-This is complete data loss for any agent that carries a prov:value attribute.</t>
+          <t>prov:value completely dropped on Agent elements. prov:value is a defined PROV-DM attribute for elements. The data is read in but not written back out on agents specifically.</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1211,9 +1270,9 @@
           <t>3.1.2-10_agent_multivalue_attr</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
@@ -1225,28 +1284,37 @@
       ]
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"agent" : {
+"ex:ag1" : {
+"ex:role" : [ "developer", "manager" ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>When an agent has an attribute with multiple xsd:string typed values, the type annotation is stripped from the output. The values survive but lose their type information, changing their meaning.</t>
+          <t>Multi-value xsd:string attributes lose type annotation on agents. When an agent has 2+ xsd:string typed values, the type information is stripped from the output. Values survive but lose their type.</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Spec §2.2, typed values</t>
+          <t>Spec Section 2.2</t>
         </is>
       </c>
     </row>
@@ -1263,44 +1331,59 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>3.1.3-03_start_time_only</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>{
+          <t>3.1.3-01_spec_example9</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
   "activity": {
     "ex:a1": {
       "prov:startTime": "2011-11-16T16:05:00",
-      "prov:type": {"$": "ex:Computation", "type": "prov:QualifiedName"}
+      "prov:endTime": "2011-11-16T16:06:00",
+      "ex:host": "server.example.org",
+      "prov:type": {
+        "$": "ex:edit",
+        "type": "prov:QualifiedName"
+      }
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"activity" : {
+"ex:a1" : {
+"prov:startTime" : "2011-11-16T16:05:00.000+01:00",
+"prov:endTime" : "2011-11-16T16:06:00.000+01:00",
+"prov:type" : [ "prov:QualifiedName", "ex:edit" ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Timestamps are silently modified during round-trip. A time like "2023-01-15T10:30:00" is rewritten as "2023-01-15T10:30:00.000+00:00".
-The spec says timestamps MUST conform to xsd:dateTime but does not explicitly require preserving the exact lexical form. However, injecting "+00:00" changes the meaning — timezone-unspecified becomes explicitly UTC. Spec Example 9 shows timestamps without timezone or milliseconds.</t>
+          <t>Timestamps silently modified — timezone injected, milliseconds added, sub-ms truncated. Spec Section 3.1.3: timestamps "MUST conform to xsd:dateTime". Injecting +00:00 changes semantic meaning: a timezone-unspecified value becomes explicitly UTC.</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Spec §3.1.3, Example 9</t>
+          <t>Spec Section 3.1.3, Example 9</t>
         </is>
       </c>
     </row>
@@ -1320,9 +1403,9 @@
           <t>B.1-01_spec_example46</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
     "prefix": {
         "ex": "http://example.org/"
     },
@@ -1348,24 +1431,24 @@
             "prov:key": "k2"
         }
     }
-}</t>
+}
+</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
+          <t>PARSE_FAILED</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>EXCEPTION: UncheckedException: Unchecked Exception
+CAUSED_BY: UnrecognizedPropertyException: Unrecognized field "hadDictionaryMember" (class org.openprovenance.prov.core.json.serialization.SortedDocument), not marked as ignorable (23 known properties: "specializationOf", "entity", "agent", "wasEndedBy", "qualifiedHadMember", "wasAttributedTo", "activity", "alternateOf", "prefix", "wasAssociatedWith", "wasInvalidatedBy", "@id", "used", "wasDerivedFrom", "bundle", "hadMember", "wasInformedBy", "wasStartedBy", "qualifiedAlternateOf", "actedOnBehalfOf", "qualifiedSpecializationOf", "wasInfluencedBy", "wasGeneratedBy")</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>The spec defines dictionary extensions in Appendix B: hadDictionaryMember (B.1), derivedByInsertionFrom (B.2), derivedByRemovalFrom (B.3), with Examples 46-52.
-ProvToolbox does not recognise any of these in JSON format. All dictionary data is silently discarded during round-trip.</t>
+          <t>PROV-Dictionary extensions not recognised in JSON format. Spec Appendix B defines hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom with Examples 46-52. All dictionary data silently discarded on round-trip.</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -1375,42 +1458,42 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>HIGH ISSUES — COMMON PATTERNS</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays instead of the spec-defined object format with "$" and "type" properties (D2.2-1). Any other spec-compliant tool reading ProvToolbox output will not recognise the typed values. Combined with non-deterministic element order (D2.2-8), the output is both incorrect and unpredictable.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Inconsistent attribute handling: Native string values behave differently depending on context — dropped when alone, kept when in an array (D2.2-7). Agent-specific attributes like prov:value are dropped entirely (D3.1.2-1), and multi-value type annotations are stripped (D3.1.2-2). These inconsistencies make it difficult to predict which data will survive a round-trip.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Timestamps semantically altered: All timestamps have timezone and milliseconds injected (D3.1.3-1). While the spec does not explicitly require exact lexical preservation, adding "+00:00" changes a timezone-unspecified time to explicitly UTC — a semantic change, not just a formatting one.</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Timestamps semantically altered: All timestamps have timezone and milliseconds injected (D3.1.3-1). Adding "+00:00" changes a timezone-unspecified time to explicitly UTC — a semantic change, not just a formatting one.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Dictionary extensions completely absent: All three PROV-Dictionary operations from Appendix B are unrecognised (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>MEDIUM ISSUES</t>
         </is>
@@ -1474,9 +1557,9 @@
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "default": "http://example.org/",
     "ex": "http://example.org/"
@@ -1490,29 +1573,47 @@
       ]
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"default" : "http://example.org/",
+"ex" : "http://example.org/"
+},
+"entity" : {
+"e1" : {
+"ex:scores" : [ {
+"type" : "xsd:int",
+"$" : "95"
+}, {
+"type" : "xsd:int",
+"$" : "87"
+}, {
+"type" : "xsd:int",
+"$" : "72"
+} ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>When an attribute has multiple values in an array, the order of values may change in the output. Array order is semantically significant in JSON.
-The spec says values MUST be collated into a JSON array but does not explicitly require preserving order.</t>
+          <t>Multi-value array order not preserved. Spec Section 2.2: multiple values "MUST be... collated in to a JSON array." Array order is semantically significant in JSON, but the spec does not explicitly require preserving it.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Spec §2.2, array collation</t>
+          <t>Spec Section 2.2</t>
         </is>
       </c>
     </row>
@@ -1532,9 +1633,9 @@
           <t>3.1.1-03_multiple_entities</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
@@ -1545,48 +1646,66 @@
     "ex:e4": {},
     "ex:e5": {"prov:label": {"$": "Fifth", "lang": "en"}}
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"entity" : {
+"ex:e4" : { },
+"ex:e1" : {
+"prov:type" : [ "ex:Document", "prov:QUALIFIED_NAME" ]
+},
+"ex:e3" : {
+"prov:type" : [ "prov:QUALIFIED_NAME", "ex:Report" ]
+},
+"ex:e2" : {
+"prov:type" : [ "ex:Image", "prov:QUALIFIED_NAME" ]
+},
+"ex:e5" : {
+"prov:label" : [ "Fifth", "en" ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>The order of elements within sections (e.g., the order of entities within the "entity" object) is not preserved. JSON object key order is not guaranteed by the JSON specification, but many systems depend on it in practice.
-The data is intact but the structure changes.</t>
+          <t>Element order within sections not preserved. JSON object key order is not guaranteed by the JSON specification, however many systems depend on it in practice.</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>JSON RFC 8259, unordered objects</t>
+          <t>JSON specification</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>MEDIUM ISSUES — COMMON PATTERNS</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Ordering not preserved: Both value order within multi-value attributes (D2.2-4) and element order within sections (D3.1.1-4) may change. While JSON object key order is not guaranteed by the JSON specification, array order is semantically significant. These changes may cause issues with systems that depend on consistent ordering.</t>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Ordering not preserved: Both value order within multi-value attributes (D2.2-4) and element order within sections (D3.1.1-4) may change. While JSON object key order is not guaranteed by the JSON specification, array order is semantically significant.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>LOW ISSUES</t>
         </is>
@@ -1650,9 +1769,9 @@
           <t>3.1.1-08_duplicate_entity_id</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
@@ -1666,23 +1785,33 @@
       "ex:note": {"$": "I am the second", "type": "xsd:string"}
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"entity" : {
+"ex:e1" : {
+"ex:note" : [ "I am the second", "xsd:string" ],
+"prov:type" : [ "prov:QUALIFIED_NAME", "ex:Second" ]
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>When the input JSON contains duplicate keys (same entity ID appearing twice), only the last occurrence is kept. This is standard JSON parser behaviour per RFC 8259 and not specific to ProvToolbox.</t>
+          <t>Duplicate JSON keys — last wins silently. Standard JSON parser behaviour per RFC 8259; not specific to ProvToolbox.</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
@@ -1707,9 +1836,9 @@
           <t>3.1.1-20_prov_role</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
@@ -1718,28 +1847,35 @@
       "prov:role": {"$": "ex:InputData", "type": "prov:QUALIFIED_NAME"}
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"entity" : {
+"ex:e1" : { }
+}
 }</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>prov:role is silently dropped when used on elements (entities, agents, activities). PROV-DM defines prov:role for relations, not elements — but elements can have arbitrary additional attributes, so prov:role should still be preserved as a generic attribute.</t>
+          <t>prov:role silently dropped on elements. PROV-DM defines prov:role for relations, not elements. Elements can have arbitrary additional attributes, so prov:role should be preserved as a generic attribute.</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>PROV-DM attribute scope</t>
+          <t>PROV-DM</t>
         </is>
       </c>
     </row>
@@ -1759,35 +1895,39 @@
           <t>3.1.1-12_empty_entity_section</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>{
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
   "entity": {}
+}
+</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+}
 }</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Empty statement sections (e.g., "entity": {}) are dropped from the output. The spec does not explicitly require preserving empty sections. No provenance data is lost.</t>
+          <t>Empty statement sections dropped from output. The spec shows sections containing data; it does not explicitly require preserving empty sections. No data loss.</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Not addressed in spec</t>
+          <t>Spec examples</t>
         </is>
       </c>
     </row>
@@ -1804,76 +1944,92 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>3.2.2-02_named_minimal</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>{
+          <t>3.2.2-01_spec_example13</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
   "prefix": {
     "ex": "http://example.org/"
   },
   "used": {
+    "_:u1": {
+      "prov:entity": "ex:e1",
+      "prov:activity": "ex:a1",
+      "ex:parameter": "p1",
+      "prov:time": "2011-11-16T16:00:00"
+    },
     "ex:use1": {
-      "prov:entity": "ex:e1",
-      "prov:activity": "ex:a1"
+      "prov:entity": "ex:e2",
+      "prov:activity": "ex:a1",
+      "ex:parameter": "p2",
+      "prov:time": "2011-11-16T16:00:01"
     }
   }
+}
+</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"used" : {
+"_:n0" : {
+"prov:activity" : "ex:a1",
+"prov:entity" : "ex:e1",
+"prov:time" : "2011-11-16T16:00:00.000+01:00"
+},
+"ex:use1" : {
+"prov:activity" : "ex:a1",
+"prov:entity" : "ex:e2",
+"prov:time" : "2011-11-16T16:00:01.000+01:00"
+}
+}
 }</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>Error: Could not find or load main class JsonRoundTrip
-Caused by: java.lang.ClassNotFoundException: JsonRoundTrip</t>
-        </is>
-      </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>The order of properties within relation objects (e.g., "prov:entity" before "prov:activity" vs the reverse) is changed in the output. JSON object key order is not guaranteed. Data is intact but JSON structure differs.</t>
+          <t>Property order within relation objects changed from input. JSON object key order is not guaranteed. Data is intact but structure differs.</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>JSON RFC 8259, unordered objects</t>
+          <t>JSON specification</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>LOW ISSUES — COMMON PATTERNS</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Minor structural differences: These involve cosmetic changes to the JSON output — property ordering, empty section omission, duplicate key handling, and prov:role scope. No provenance data is lost. They may cause issues with strict byte-for-byte comparison but do not affect semantic content.</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Minor structural differences: These involve cosmetic changes to the JSON output — property ordering, empty section omission, duplicate key handling, and prov:role scope. No provenance data is lost.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A45:H45"/>
+  <mergeCells count="8">
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
   </mergeCells>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -515,10 +515,10 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -621,9 +621,16 @@
 }</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Native JSON values silently dropped as sole attribute values. The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox drops them silently — the attribute disappears from the output.</t>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Native values inside arrays survive. "ex:tags": ["alpha","beta","gamma"] comes back (reordered but present).
+WHAT BREAKS: A native value as the SOLE value of an attribute is silently dropped. Tested all three JSON types:
+  "ex:name": "hello" (string) -&gt; entity becomes { } — attribute gone
+  "ex:count": 42 (integer) -&gt; entity becomes { } — attribute gone
+  "ex:flag": true (boolean) -&gt; entity becomes { } — attribute gone
+  "ex:amount": -99.5 (negative float) -&gt; entity becomes { } — attribute gone
+Even with xsd prefix explicitly declared (test 2.2-28), same result.
+Tests: 2.2-04 (string), 2.2-05 (int), 2.2-06 (float), 2.2-07 (bool), 2.2-08 (negative), 2.2-20 (bool false), 2.2-28 (string+xsd prefix).</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -678,9 +685,14 @@
           <t>EXCEPTION: UncheckedException: Unchecked Exception</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Native number/boolean in mixed arrays crash the serialiser. Spec Section 2.2 Example 3 explicitly shows an array mixing typed values and a plain integer 2. ProvToolbox parses this OK but crashes with UncheckedException when serialising back.</t>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Array of only typed objects serialises (wrong format, but no crash). Array of only native strings also survives.
+WHAT BREAKS: Mix typed objects with native values in the same array — serialiser crashes.
+Input (spec's own Example 3): "ex:tag": [{"$":"hello","type":"xsd:string"}, 2, {"$":"Qk0=","type":"xsd:base64Binary"}]
+Result: SERIALIZE_FAILED — JsonMappingException: unknown value type null
+ProvToolbox reads the mixed array fine. It crashes only when trying to write it back. The serialiser doesn't know how to handle the native value it already parsed.
+Also crashes: 2.2-12 (typed+native bool), 2.2-22 (array of native ints [1,2,3]).</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -741,9 +753,19 @@
 }</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>prov:value loses its data content on round-trip. prov:value is a defined PROV-DM attribute for holding the actual content/value of an entity. The data is read in successfully but not written back out.</t>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: The prov:value KEY survives in output. The type name sometimes survives.
+WHAT BREAKS: The actual DATA CONTENT (the "$" value) is dropped.
+  Input: "prov:value": {"$":"42", "type":"xsd:int"}
+  Output: "prov:value": ["xsd:int"]  — "42" is gone
+  Input: "prov:value": {"$":"some text content", "type":"xsd:string"}
+  Output: "prov:value": ["xsd:string"]  — text content gone
+Inconsistency: test 3.1.1-18 (no prefix for type) — the VALUE survives but TYPE is dropped:
+  Input: {"$":"the actual content", "type":"xsd:string"}
+  Output: ["the actual content"]  — type gone, value kept
+On agents and activities it is even worse — entire prov:value disappears (see D3.1.2-1).
+Tests: 2.2-15, 2.2-23, 3.1.1-18, 3.1.1-22.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -796,9 +818,11 @@
 CAUSED_BY: NullPointerException: Cannot invoke "java.util.Collection.iterator()" because "attributes" is null</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>JSON null as attribute value crashes the parser with an unhandled NullPointerException. While null is not a defined PROV-JSON value type, the parser should reject it with a clean error message, not an unhandled crash.</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>null is not a valid PROV-JSON value type, so rejection is correct.
+WHAT BREAKS: Instead of a clean error message like "invalid value type at line X", the parser crashes with an unhandled NullPointerException.
+This test passes our suite (we expected PARSE_FAILED), but the crash quality is the issue — any robust parser should give a meaningful error, not an unhandled NPE.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -850,9 +874,18 @@
 CAUSED_BY: NullPointerException: Cannot invoke "org.openprovenance.prov.model.QualifiedName.getPrefix()" because "this.id" is null</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Bundle deserialisation completely broken. Every single bundle test crashes with NullPointerException. Bundles are the primary mechanism for grouping and attributing provenance (Section 3.3).</t>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Nothing. 6 out of 6 bundle tests crash. Also A.3-01 (spec Example 44 with bundle).
+WHAT BREAKS: Every bundle, no matter how simple:
+  3.3-01: Minimal bundle (one entity inside) -&gt; NPE
+  3.3-02: Bundle with a relation -&gt; NPE
+  3.3-03: Top-level statements + bundle -&gt; NPE
+  3.3-04: Multiple bundles -&gt; NPE
+  3.3-05: Empty bundle (no statements) -&gt; NPE
+  3.3-06: Bundle with own prefix section -&gt; NPE
+All crash with: NullPointerException: Cannot invoke "QualifiedName.getPrefix()" because "this.id" is null
+The deserialiser fails to set the bundle's id field before Jackson tries to call getPrefix() on it.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -871,14 +904,14 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox either drops them silently (D2.2-2) or crashes when they appear in mixed arrays (D2.2-3). Combined with prov:value being lost (D2.2-5), any provenance document using the simpler value formats will lose data.</t>
+          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox drops them when they are the sole attribute value (D2.2-2), crashes when they appear in mixed arrays with typed objects (D2.2-3), and loses prov:value content (D2.2-5). Any provenance document using the simpler value formats will lose data.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Bundles completely non-functional: Every single bundle test crashes (D3.3-1). Bundles are the primary mechanism for grouping and attributing provenance — this blocks a core use case of PROV-JSON.</t>
+          <t>Bundles completely non-functional: Every single bundle test crashes with NPE (D3.3-1) — the deserialiser fails to set the bundle ID before Jackson calls getPrefix(). Bundles are the primary mechanism for grouping and attributing provenance. This blocks a core use case of PROV-JSON.</t>
         </is>
       </c>
     </row>
@@ -978,9 +1011,13 @@
 }</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>User-defined "_" prefix silently overridden by internal blank node mapping. The spec defines "_:" for blank node identifiers per Turtle nodeID production. A user-defined "_" namespace prefix is silently overwritten.</t>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All other user-defined prefixes ("ex", "custom", "myprefix") are preserved fine.
+WHAT BREAKS: Only the "_" prefix specifically.
+  Input prefix: "_": "http://example.org/my-blanks/"
+  Output: the "_" prefix is gone entirely — not in the prefix section at all
+ProvToolbox internally uses "_:" for blank nodes (per spec), but instead of co-existing with a user's "_" prefix, it overwrites it silently. No warning, no error.</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1045,9 +1082,19 @@
 }</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Typed values serialised as 2-element arrays instead of {"$":..., "type":...} objects. The spec defines typed values as JSON objects with "$" and "type" properties. ProvToolbox outputs [value, type] arrays instead.</t>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: The data content and type name both survive (usually).
+WHAT BREAKS: The FORMAT is wrong. Spec defines typed values as JSON objects; ProvToolbox outputs 2-element arrays.
+  Spec format:     {"$": "1034", "type": "xsd:positiveInteger"}
+  ProvToolbox out: ["xsd:positiveInteger", "1034"]
+  Spec format:     {"$": "36.6", "type": "xsd:float"}
+  ProvToolbox out: ["xsd:float", "36.6"]
+  Spec format:     {"$": "Londres", "lang": "fr"}
+  ProvToolbox out: ["Londres", "fr"]
+The lang-tagged case also becomes an array — so there is no way to distinguish a language tag from a type in ProvToolbox's output.
+Any other spec-compliant tool reading this output will fail to parse typed values.
+Affects almost every test with typed attributes (60+ tests).</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1108,9 +1155,15 @@
 }</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Native strings behave differently depending on context. When a native string is the sole attribute value, it is dropped (D2.2-2). When in an array, it survives. The spec allows native types equally in both contexts.</t>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Native strings in an array survive:
+  Input:  "ex:tags": ["alpha", "beta", "gamma"]
+  Output: "ex:tags": ["beta", "alpha", "gamma"]  — present but reordered
+WHAT BREAKS: A native string as sole value is dropped (D2.2-2):
+  Input:  "ex:name": "hello"
+  Output: entity becomes { }  — attribute gone
+Same data type, same spec permission. The only difference is whether it is the sole value or one of many in an array.</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -1184,9 +1237,12 @@
 }</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>2-element array output has non-deterministic element order. The [value, type] arrays from D2.2-1 have unpredictable element order depending on Java hash codes, making the already-incorrect format additionally unreliable.</t>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>The [value, type] arrays from D2.2-1 do not have consistent element order. From the SAME test, SAME entity:
+  "ex:byteSize"    -&gt; ["xsd:positiveInteger", "1034"]     (type first)
+  "ex:compression" -&gt; ["82.5e-2", "xsd:double"]           (value first)
+The order depends on Java's internal hash codes for the strings. So a consumer cannot even rely on position to tell value from type.</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -1243,9 +1299,19 @@
 }</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>prov:value completely dropped on Agent elements. prov:value is a defined PROV-DM attribute for elements. The data is read in but not written back out on agents specifically.</t>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: On entities, prov:value partially works (key survives, content often lost — see D2.2-5).
+WHAT BREAKS: On agents and activities, the ENTIRE prov:value attribute disappears:
+  Entity input:   "prov:value": {"$":"42","type":"xsd:int"}
+  Entity output:  "prov:value": ["xsd:int"]  — key survives, content lost
+  Agent input:    "prov:value": {"$":"agent-data-123","type":"xsd:string"}
+  Agent output:   "ex:ag1": { }  — ENTIRE attribute gone
+  Agent input:    "prov:value": {"$":"42","type":"xsd:int"}
+  Agent output:   "ex:ag1": { }  — ENTIRE attribute gone
+  Activity input: "prov:value": {"$":"computation-result","type":"xsd:string"}
+  Activity output: "ex:a1": { }  — ENTIRE attribute gone
+Tests: 3.1.2-06, 3.1.2-13 (agents), 3.1.3-07 (activity).</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1307,9 +1373,13 @@
 }</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Multi-value xsd:string attributes lose type annotation on agents. When an agent has 2+ xsd:string typed values, the type information is stripped from the output. Values survive but lose their type.</t>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: A single typed value on an agent keeps its type (as wrong array format).
+WHAT BREAKS: Two or more xsd:string values on the same attribute — type stripped:
+  Input:  "ex:role": [{"$":"developer","type":"xsd:string"}, {"$":"manager","type":"xsd:string"}]
+  Output: "ex:role": ["developer", "manager"]
+Values survive. Type annotations gone. You cannot tell if these were typed xsd:string or plain native strings.</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -1376,9 +1446,16 @@
 }</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Timestamps silently modified — timezone injected, milliseconds added, sub-ms truncated. Spec Section 3.1.3: timestamps "MUST conform to xsd:dateTime". Injecting +00:00 changes semantic meaning: a timezone-unspecified value becomes explicitly UTC.</t>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Pre-formatted timestamps matching ProvToolbox's own output format round-trip perfectly. Test 3.1.3-13 passes with "2011-11-16T16:05:00.000+01:00".
+WHAT BREAKS: Any other valid xsd:dateTime format is modified:
+  "2011-11-16T16:05:00"        -&gt; "2011-11-16T16:05:00.000+01:00"  (added .000 and local TZ)
+  "2011-11-16T16:05:00Z"       -&gt; "2011-11-16T16:05:00.000Z"       (added .000)
+  "2011-11-16T16:06:00.456789Z"-&gt; "2011-11-16T16:06:00.456Z"       (truncated microseconds)
+  "2011-11-16" (date only)     -&gt; "2011-11-16T00:00:00.000+01:00"  (added time, ms, local TZ)
+The +01:00 is the MACHINE'S LOCAL TIMEZONE — same input produces different output depending on where you run it. Adding a timezone changes semantic meaning: "unspecified timezone" becomes "explicitly UTC+1".
+Tests: 3.1.3-01 through 3.1.3-12 (except 3.1.3-13 which passes), 3.1.3-14.</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -1446,9 +1523,15 @@
 CAUSED_BY: UnrecognizedPropertyException: Unrecognized field "hadDictionaryMember" (class org.openprovenance.prov.core.json.serialization.SortedDocument), not marked as ignorable (23 known properties: "specializationOf", "entity", "agent", "wasEndedBy", "qualifiedHadMember", "wasAttributedTo", "activity", "alternateOf", "prefix", "wasAssociatedWith", "wasInvalidatedBy", "@id", "used", "wasDerivedFrom", "bundle", "hadMember", "wasInformedBy", "wasStartedBy", "qualifiedAlternateOf", "actedOnBehalfOf", "qualifiedSpecializationOf", "wasInfluencedBy", "wasGeneratedBy")</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>PROV-Dictionary extensions not recognised in JSON format. Spec Appendix B defines hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom with Examples 46-52. All dictionary data silently discarded on round-trip.</t>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All standard PROV relations (wasGeneratedBy, used, wasDerivedFrom, etc.) parse fine.
+WHAT BREAKS: The three dictionary-specific relation types from Appendix B:
+  hadDictionaryMember    (Example 46) -&gt; UnrecognizedPropertyException
+  derivedByInsertionFrom (Example 48) -&gt; UnrecognizedPropertyException
+  derivedByRemovalFrom   (Example 52) -&gt; UnrecognizedPropertyException
+The error message lists all 23 fields the deserialiser DOES recognise — dictionary types are not among them. The SortedDocument class simply has no fields for dictionary operations.
+Tests: B.1-01, B.2-01, B.3-01.</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -1467,28 +1550,28 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays instead of the spec-defined object format with "$" and "type" properties (D2.2-1). Any other spec-compliant tool reading ProvToolbox output will not recognise the typed values. Combined with non-deterministic element order (D2.2-8), the output is both incorrect and unpredictable.</t>
+          <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays ["value","type"] instead of the spec-defined object format {"$":"value","type":"..."} (D2.2-1). The element order within these arrays is also non-deterministic (D2.2-8) — sometimes type-first, sometimes value-first, depending on Java hash codes. Any other spec-compliant tool reading ProvToolbox output will not recognise the typed values.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Inconsistent attribute handling: Native string values behave differently depending on context — dropped when alone, kept when in an array (D2.2-7). Agent-specific attributes like prov:value are dropped entirely (D3.1.2-1), and multi-value type annotations are stripped (D3.1.2-2). These inconsistencies make it difficult to predict which data will survive a round-trip.</t>
+          <t>Inconsistent attribute handling across element types: Native string values are dropped when alone but kept in arrays (D2.2-7). prov:value partially works on entities (key survives, content lost) but is entirely dropped on agents and activities (D3.1.2-1). Multi-value xsd:string types are stripped on agents (D3.1.2-2). The behaviour depends on which element type the attribute is on and how many values it has.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Timestamps semantically altered: All timestamps have timezone and milliseconds injected (D3.1.3-1). Adding "+00:00" changes a timezone-unspecified time to explicitly UTC — a semantic change, not just a formatting one.</t>
+          <t>Timestamps semantically altered: All timestamps are forced into ProvToolbox's internal format — milliseconds added, microseconds truncated, and the MACHINE'S LOCAL TIMEZONE injected (D3.1.3-1). "2011-11-16T16:05:00" (no timezone) becomes "2011-11-16T16:05:00.000+01:00" (explicitly local time). Same input produces different output on different machines.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Dictionary extensions completely absent: All three PROV-Dictionary operations from Appendix B are unrecognised (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
+          <t>Dictionary extensions completely absent: All three PROV-Dictionary operations from Appendix B are unrecognised by the deserialiser — the SortedDocument class has no fields for them (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
         </is>
       </c>
     </row>
@@ -1606,9 +1689,13 @@
 }</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>Multi-value array order not preserved. Spec Section 2.2: multiple values "MUST be... collated in to a JSON array." Array order is semantically significant in JSON, but the spec does not explicitly require preserving it.</t>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Single values stay in place.
+WHAT BREAKS: Multi-value arrays get reordered:
+  Input:  ["alpha", "beta", "gamma"]
+  Output: ["beta", "alpha", "gamma"]
+Content survives, order does not. Array order is semantically significant in JSON, but the spec does not explicitly require preserving it.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -1679,9 +1766,13 @@
 }</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>Element order within sections not preserved. JSON object key order is not guaranteed by the JSON specification, however many systems depend on it in practice.</t>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Data within each element is complete.
+WHAT BREAKS: Element ordering within sections changes:
+  Input order:  "ex:e1", "ex:e2", "ex:e3"
+  Output order: may become "ex:e3", "ex:e1", "ex:e2"
+JSON object key order is not guaranteed by the JSON spec, so this is debatable, but many systems depend on it in practice.</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -1700,7 +1791,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Ordering not preserved: Both value order within multi-value attributes (D2.2-4) and element order within sections (D3.1.1-4) may change. While JSON object key order is not guaranteed by the JSON specification, array order is semantically significant.</t>
+          <t>Ordering not preserved: Multi-value arrays get reordered (D2.2-4) — content survives but position changes. Element keys within sections are also shuffled (D3.1.1-4). JSON object key order is not guaranteed by the JSON spec, but array order is semantically significant.</t>
         </is>
       </c>
     </row>
@@ -1809,9 +1900,9 @@
 }</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>Duplicate JSON keys — last wins silently. Standard JSON parser behaviour per RFC 8259; not specific to ProvToolbox.</t>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate JSON keys in the same object — last one wins silently. This is standard JSON parser behaviour per RFC 8259, not specific to ProvToolbox.</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
@@ -1868,9 +1959,10 @@
 }</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>prov:role silently dropped on elements. PROV-DM defines prov:role for relations, not elements. Elements can have arbitrary additional attributes, so prov:role should be preserved as a generic attribute.</t>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: prov:role on relations (wasGeneratedBy, wasAssociatedWith, etc.) is preserved. Test 3.2.1-05 and 3.2.9-03 show prov:role surviving on relations (wrong array format, but data is there).
+WHAT BREAKS: prov:role on elements (entity, agent, activity) is dropped. PROV-DM defines prov:role for relations, not elements, so dropping it on elements is arguably correct — but it could be preserved as a generic attribute.</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -1920,9 +2012,10 @@
 }</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>Empty statement sections dropped from output. The spec shows sections containing data; it does not explicitly require preserving empty sections. No data loss.</t>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Sections with actual data are always present.
+WHAT BREAKS: Empty sections like "entity": {} are dropped from output entirely. No data was in them, so no data is lost. Cosmetic difference only.</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
@@ -1997,9 +2090,9 @@
 }</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>Property order within relation objects changed from input. JSON object key order is not guaranteed. Data is intact but structure differs.</t>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Property order within relation objects is changed from input. For example, "prov:entity" and "prov:activity" keys may swap positions. JSON object key order is not guaranteed. Data is intact, only structure differs.</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -2018,7 +2111,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Minor structural differences: These involve cosmetic changes to the JSON output — property ordering, empty section omission, duplicate key handling, and prov:role scope. No provenance data is lost.</t>
+          <t>Minor structural differences: Duplicate keys use last-wins (standard JSON behaviour, D3.1.1-5). prov:role is dropped on elements but preserved on relations (D3.1.1-7). Empty sections are omitted (D3.1.1-8). Property order within relation objects changes (D3.2.2-1). No provenance data is lost in any of these cases.</t>
         </is>
       </c>
     </row>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -509,17 +509,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,6 +569,11 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Workaround</t>
         </is>
       </c>
     </row>
@@ -623,19 +629,28 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: Native values inside arrays survive. "ex:tags": ["alpha","beta","gamma"] comes back (reordered but present).
-WHAT BREAKS: A native value as the SOLE value of an attribute is silently dropped. Tested all three JSON types:
-  "ex:name": "hello" (string) -&gt; entity becomes { } — attribute gone
-  "ex:count": 42 (integer) -&gt; entity becomes { } — attribute gone
-  "ex:flag": true (boolean) -&gt; entity becomes { } — attribute gone
-  "ex:amount": -99.5 (negative float) -&gt; entity becomes { } — attribute gone
-Even with xsd prefix explicitly declared (test 2.2-28), same result.
-Tests: 2.2-04 (string), 2.2-05 (int), 2.2-06 (float), 2.2-07 (bool), 2.2-08 (negative), 2.2-20 (bool false), 2.2-28 (string+xsd prefix).</t>
+          <t>WHAT WORKS: Typed values like {"$":"hello","type":"xsd:string"} are accepted.
+WHAT BREAKS: Native JSON values ("hello", 42, true) used directly as attribute values are silently dropped. The entity appears in output but the attribute is gone.
+ROOT CAUSE: CustomAttributeSetDeserializer.java line 45 calls next.textValue() which returns null for non-string native JSON types.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Spec Section 2.2, "MAY" keyword</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS INPUT: Convert all native JSON attribute values to the explicit typed format before passing to ProvToolbox.
+Instead of:
+  "ex:name": "hello"
+Use:
+  "ex:name": [{"$": "hello", "type": "xsd:string"}]
+Instead of:
+  "ex:count": 42
+Use:
+  "ex:count": [{"$": "42", "type": "xsd:int"}]
+A simple JSON pre-processor can do this automatically.</t>
         </is>
       </c>
     </row>
@@ -687,17 +702,24 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: Array of only typed objects serialises (wrong format, but no crash). Array of only native strings also survives.
-WHAT BREAKS: Mix typed objects with native values in the same array — serialiser crashes.
-Input (spec's own Example 3): "ex:tag": [{"$":"hello","type":"xsd:string"}, 2, {"$":"Qk0=","type":"xsd:base64Binary"}]
-Result: SERIALIZE_FAILED — JsonMappingException: unknown value type null
-ProvToolbox reads the mixed array fine. It crashes only when trying to write it back. The serialiser doesn't know how to handle the native value it already parsed.
-Also crashes: 2.2-12 (typed+native bool), 2.2-22 (array of native ints [1,2,3]).</t>
+          <t>WHAT WORKS: Arrays containing only typed value objects ({"$":...,"type":...}) are processed.
+WHAT BREAKS: Mixing native JSON values (plain integers, booleans) with typed objects in the same array crashes the serialiser with UncheckedException.
+ROOT CAUSE: Same as D2.2-2 — native values in arrays create broken internal attributes that crash during serialization.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Spec Section 2.2, Example 3</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS INPUT: Same as D2.2-2 — convert all native values in arrays to typed format.
+Instead of:
+  "ex:attr": [{"$":"a","type":"xsd:string"}, 2]
+Use:
+  "ex:attr": [{"$":"a","type":"xsd:string"}, {"$":"2","type":"xsd:int"}]
+This eliminates the crash entirely.</t>
         </is>
       </c>
     </row>
@@ -755,22 +777,21 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: The prov:value KEY survives in output. The type name sometimes survives.
-WHAT BREAKS: The actual DATA CONTENT (the "$" value) is dropped.
-  Input: "prov:value": {"$":"42", "type":"xsd:int"}
-  Output: "prov:value": ["xsd:int"]  — "42" is gone
-  Input: "prov:value": {"$":"some text content", "type":"xsd:string"}
-  Output: "prov:value": ["xsd:string"]  — text content gone
-Inconsistency: test 3.1.1-18 (no prefix for type) — the VALUE survives but TYPE is dropped:
-  Input: {"$":"the actual content", "type":"xsd:string"}
-  Output: ["the actual content"]  — type gone, value kept
-On agents and activities it is even worse — entire prov:value disappears (see D3.1.2-1).
-Tests: 2.2-15, 2.2-23, 3.1.1-18, 3.1.1-22.</t>
+          <t>WHAT WORKS: prov:value is parsed and stored internally — the data IS read in.
+WHAT BREAKS: prov:value is not written back out. The attribute disappears from the serialized output.
+ROOT CAUSE: JSON_Entity.java line 12 has @JsonIgnore on getValue(), telling Jackson to skip prov:value during serialization.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>PROV-DM attribute definition</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS INPUT: Rename "prov:value" to a custom attribute (e.g., "ex:provValue") before passing to ProvToolbox.
+POST-PROCESS OUTPUT: Rename it back to "prov:value" in the output.
+Alternatively, use a different serialization format (PROV-N) for documents that need prov:value preserved.</t>
         </is>
       </c>
     </row>
@@ -820,14 +841,21 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>null is not a valid PROV-JSON value type, so rejection is correct.
-WHAT BREAKS: Instead of a clean error message like "invalid value type at line X", the parser crashes with an unhandled NullPointerException.
-This test passes our suite (we expected PARSE_FAILED), but the crash quality is the issue — any robust parser should give a meaningful error, not an unhandled NPE.</t>
+          <t>WHAT WORKS: All other JSON value types (string, number, boolean, object, array) as attribute values.
+WHAT BREAKS: JSON null as an attribute value crashes the parser with NullPointerException.
+ROOT CAUSE: CustomAttributeSetDeserializer.java — null JSON nodes produce null text values, causing NPE in attribute creation.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Defensive error handling</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS INPUT: Validate JSON and remove or replace null attribute values before passing to ProvToolbox.
+Example: scan all attribute values and either remove null entries or replace with an empty string typed value:
+  null  →  {"$": "", "type": "xsd:string"}</t>
         </is>
       </c>
     </row>
@@ -876,111 +904,132 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: Nothing. 6 out of 6 bundle tests crash. Also A.3-01 (spec Example 44 with bundle).
-WHAT BREAKS: Every bundle, no matter how simple:
-  3.3-01: Minimal bundle (one entity inside) -&gt; NPE
-  3.3-02: Bundle with a relation -&gt; NPE
-  3.3-03: Top-level statements + bundle -&gt; NPE
-  3.3-04: Multiple bundles -&gt; NPE
-  3.3-05: Empty bundle (no statements) -&gt; NPE
-  3.3-06: Bundle with own prefix section -&gt; NPE
-All crash with: NullPointerException: Cannot invoke "QualifiedName.getPrefix()" because "this.id" is null
-The deserialiser fails to set the bundle's id field before Jackson tries to call getPrefix() on it.</t>
+          <t>WHAT WORKS: Top-level statements (entities, activities, etc.) outside bundles work fine.
+WHAT BREAKS: Every single bundle test crashes with NullPointerException. Bundles cannot be deserialized at all.
+ROOT CAUSE: SortedBundle.java line 299 — when deferredId=true, toBundle() tries to call id.getPrefix() but id is null because the bundle name was used as a map KEY but never set on the SortedBundle object during deserialization.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Spec Section 3.3, Examples 40-41</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>NO IN-FORMAT WORKAROUND — bundles are completely non-functional in PROV-JSON.
+Options:
+1. EXTRACT BUNDLES: Pre-process the JSON to extract each bundle's statements as a separate standalone document. Round-trip each individually, then manually reassemble.
+2. USE PROV-N FORMAT: Use ProvToolbox's PROV-N serializer instead, which handles bundles correctly.
+3. FLATTEN: If bundle boundaries are not critical, flatten all statements to top-level.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL ISSUES — COMMON PATTERNS</t>
+          <t>CRITICAL ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox drops them when they are the sole attribute value (D2.2-2), crashes when they appear in mixed arrays with typed objects (D2.2-3), and loses prov:value content (D2.2-5). Any provenance document using the simpler value formats will lose data.</t>
+          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox either drops them silently (D2.2-2) or crashes when they appear in mixed arrays (D2.2-3). Combined with prov:value being lost (D2.2-5), any provenance document using the simpler value formats will lose data.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Bundles completely non-functional: Every single bundle test crashes with NPE (D3.3-1) — the deserialiser fails to set the bundle ID before Jackson calls getPrefix(). Bundles are the primary mechanism for grouping and attributing provenance. This blocks a core use case of PROV-JSON.</t>
+          <t>WORKAROUND AVAILABLE for native values (D2.2-2, D2.2-3, D2.2-5): Pre-process input JSON to convert all native values to explicit typed format, and rename prov:value to a custom attribute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Bundles completely non-functional: Every single bundle test crashes (D3.3-1). Bundles are the primary mechanism for grouping and attributing provenance — this blocks a core use case of PROV-JSON.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>NO WORKAROUND for bundles (D3.3-1): Must extract bundle contents into separate documents or use PROV-N format instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>HIGH ISSUES</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Issue ID</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Input JSON (what we sent)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Output / Error (what we got back)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Problem Description</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Spec Reference</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Workaround</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>D2.1-7</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>2.1-12_user_underscore_prefix</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -994,12 +1043,12 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1011,38 +1060,46 @@
 }</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All other user-defined prefixes ("ex", "custom", "myprefix") are preserved fine.
-WHAT BREAKS: Only the "_" prefix specifically.
-  Input prefix: "_": "http://example.org/my-blanks/"
-  Output: the "_" prefix is gone entirely — not in the prefix section at all
-ProvToolbox internally uses "_:" for blank nodes (per spec), but instead of co-existing with a user's "_" prefix, it overwrites it silently. No warning, no error.</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All other user-defined namespace prefixes ("ex:", "foaf:", "custom:", etc.).
+WHAT BREAKS: Using "_" as a namespace prefix — it gets silently overwritten by ProvToolbox's internal blank node mapping to "https://openprovenance.org/blank#".
+ROOT CAUSE: SortedBundle.java lines 36-37 hardcode bnPrefix="_" and bnNS="https://openprovenance.org/blank#".</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.1</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS INPUT: Avoid using "_" as a namespace prefix. Rename it to something else (e.g., "underscore", "bnk", "u") in both:
+1. The "prefix" section
+2. All qualified names using that prefix
+Example:
+  "_": "http://example.org/ns/"  →  "u": "http://example.org/ns/"
+  "_:foo"  →  "u:foo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>D2.2-1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>2.2-01_spec_example1_typed</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1060,12 +1117,12 @@
 </t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1082,44 +1139,45 @@
 }</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: The data content and type name both survive (usually).
-WHAT BREAKS: The FORMAT is wrong. Spec defines typed values as JSON objects; ProvToolbox outputs 2-element arrays.
-  Spec format:     {"$": "1034", "type": "xsd:positiveInteger"}
-  ProvToolbox out: ["xsd:positiveInteger", "1034"]
-  Spec format:     {"$": "36.6", "type": "xsd:float"}
-  ProvToolbox out: ["xsd:float", "36.6"]
-  Spec format:     {"$": "Londres", "lang": "fr"}
-  ProvToolbox out: ["Londres", "fr"]
-The lang-tagged case also becomes an array — so there is no way to distinguish a language tag from a type in ProvToolbox's output.
-Any other spec-compliant tool reading this output will fail to parse typed values.
-Affects almost every test with typed attributes (60+ tests).</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Typed values are parsed correctly — the data survives the round-trip.
+WHAT BREAKS: The output format is wrong. Spec defines {"$":"1034","type":"xsd:positiveInteger"} but ProvToolbox outputs ["xsd:positiveInteger","1034"] — a 2-element array instead of an object.
+ROOT CAUSE: The serializer outputs typed values as flat [type, value] arrays instead of using the spec-defined object format with "$" and "type" properties.</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2, "$" and "type" properties</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>POST-PROCESS OUTPUT: Convert 2-element arrays in attribute positions back to spec-compliant objects.
+Detection: In attribute positions, a 2-element array where one element contains ":" (type name) is a typed value.
+Conversion:
+  ["xsd:positiveInteger", "1034"]  →  {"$": "1034", "type": "xsd:positiveInteger"}
+A JSON post-processor can walk the output and fix all typed value arrays automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>D2.2-7</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>2.2-19_native_string_array</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1135,12 +1193,12 @@
 </t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1155,40 +1213,44 @@
 }</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Native strings in an array survive:
-  Input:  "ex:tags": ["alpha", "beta", "gamma"]
-  Output: "ex:tags": ["beta", "alpha", "gamma"]  — present but reordered
-WHAT BREAKS: A native string as sole value is dropped (D2.2-2):
-  Input:  "ex:name": "hello"
-  Output: entity becomes { }  — attribute gone
-Same data type, same spec permission. The only difference is whether it is the sole value or one of many in an array.</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Native strings survive when they appear inside arrays alongside typed values.
+WHAT BREAKS: Native strings are dropped when they are the sole attribute value (not in an array).
+ROOT CAUSE: Different code paths handle sole values vs array elements. The array path processes strings correctly, but sole native values are lost.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS INPUT: Same as D2.2-2 — always use typed format for all values.
+Alternatively, wrap sole native values in an array:
+  "ex:name": "hello"  →  "ex:name": ["hello"]
+But the typed format is more reliable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>D2.2-8</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1208,12 +1270,12 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1237,37 +1299,42 @@
 }</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>The [value, type] arrays from D2.2-1 do not have consistent element order. From the SAME test, SAME entity:
-  "ex:byteSize"    -&gt; ["xsd:positiveInteger", "1034"]     (type first)
-  "ex:compression" -&gt; ["82.5e-2", "xsd:double"]           (value first)
-The order depends on Java's internal hash codes for the strings. So a consumer cannot even rely on position to tell value from type.</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Data content survives — the type and value strings are both present.
+WHAT BREAKS: The 2-element [type, value] arrays (from D2.2-1) have non-deterministic element order. Sometimes type comes first, sometimes value comes first, depending on Java hash codes.
+ROOT CAUSE: Internal HashMap-based storage does not preserve insertion order.</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>POST-PROCESS OUTPUT: Same fix as D2.2-1 — convert arrays to objects. When converting, detect which element is the type vs. value by checking which contains ":" (qualified type names always contain a colon like "xsd:int").
+Heuristic: the element matching pattern "prefix:localPart" is the type; the other is the value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>3.1.2-06_agent_prov_value</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1282,12 +1349,12 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1299,44 +1366,43 @@
 }</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: On entities, prov:value partially works (key survives, content often lost — see D2.2-5).
-WHAT BREAKS: On agents and activities, the ENTIRE prov:value attribute disappears:
-  Entity input:   "prov:value": {"$":"42","type":"xsd:int"}
-  Entity output:  "prov:value": ["xsd:int"]  — key survives, content lost
-  Agent input:    "prov:value": {"$":"agent-data-123","type":"xsd:string"}
-  Agent output:   "ex:ag1": { }  — ENTIRE attribute gone
-  Agent input:    "prov:value": {"$":"42","type":"xsd:int"}
-  Agent output:   "ex:ag1": { }  — ENTIRE attribute gone
-  Activity input: "prov:value": {"$":"computation-result","type":"xsd:string"}
-  Activity output: "ex:a1": { }  — ENTIRE attribute gone
-Tests: 3.1.2-06, 3.1.2-13 (agents), 3.1.3-07 (activity).</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Other agent attributes (prov:label, prov:type, prov:location, custom attributes) are preserved.
+WHAT BREAKS: prov:value on agents is read in but not written back out — same as D2.2-5 but specifically on agent elements.
+ROOT CAUSE: JSON_Entity.java @JsonIgnore on getValue() — JSON_Agent extends JSON_Entity, inheriting the ignore.</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>PROV-DM attribute definition</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Same as D2.2-5:
+PRE-PROCESS INPUT: Rename "prov:value" to a custom attribute (e.g., "ex:provValue").
+POST-PROCESS OUTPUT: Rename back to "prov:value".</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>3.1.2-10_agent_multivalue_attr</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1354,12 +1420,12 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1373,38 +1439,42 @@
 }</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: A single typed value on an agent keeps its type (as wrong array format).
-WHAT BREAKS: Two or more xsd:string values on the same attribute — type stripped:
-  Input:  "ex:role": [{"$":"developer","type":"xsd:string"}, {"$":"manager","type":"xsd:string"}]
-  Output: "ex:role": ["developer", "manager"]
-Values survive. Type annotations gone. You cannot tell if these were typed xsd:string or plain native strings.</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Single xsd:string values retain their type annotation. Non-string typed values keep their types.
+WHAT BREAKS: When an agent has 2+ xsd:string typed values for the same attribute, the type annotation is stripped — values output as bare strings instead of typed objects.
+ROOT CAUSE: CustomTypedValueSerializer.java lines 29-31 — xsd:string with a LangString value (no lang) is output as a plain JSON string, losing the type wrapper.</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>POST-PROCESS OUTPUT: Re-wrap bare strings inside attribute arrays with {"$": "value", "type": "xsd:string"} when the original input had typed format.
+Alternatively, PRE-PROCESS: use prov:InternationalizedString type instead of xsd:string to force type preservation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>D3.1.3-1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>3.1.3-01_spec_example9</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1425,12 +1495,12 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1446,41 +1516,44 @@
 }</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Pre-formatted timestamps matching ProvToolbox's own output format round-trip perfectly. Test 3.1.3-13 passes with "2011-11-16T16:05:00.000+01:00".
-WHAT BREAKS: Any other valid xsd:dateTime format is modified:
-  "2011-11-16T16:05:00"        -&gt; "2011-11-16T16:05:00.000+01:00"  (added .000 and local TZ)
-  "2011-11-16T16:05:00Z"       -&gt; "2011-11-16T16:05:00.000Z"       (added .000)
-  "2011-11-16T16:06:00.456789Z"-&gt; "2011-11-16T16:06:00.456Z"       (truncated microseconds)
-  "2011-11-16" (date only)     -&gt; "2011-11-16T00:00:00.000+01:00"  (added time, ms, local TZ)
-The +01:00 is the MACHINE'S LOCAL TIMEZONE — same input produces different output depending on where you run it. Adding a timezone changes semantic meaning: "unspecified timezone" becomes "explicitly UTC+1".
-Tests: 3.1.3-01 through 3.1.3-12 (except 3.1.3-13 which passes), 3.1.3-14.</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Timestamps are parsed and the date/time values are preserved.
+WHAT BREAKS: Timezone "+00:00" is injected into timezone-unspecified timestamps. Milliseconds ".000" are added. Sub-millisecond precision is truncated.
+ROOT CAUSE: CustomXMLGregorianCalendarDeserializer.java line 37 — pf.newISOTime() normalizes the calendar. CustomDateSerializer.java uses d.toString() which outputs the normalized form.</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Spec Section 3.1.3, Example 9</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>PRE/POST-PROCESS:
+1. Before round-trip: extract all timestamp values from the input JSON.
+2. After round-trip: compare output timestamps with originals and restore the original format where they differ.
+Alternatively, accept the normalized format if semantic equivalence (same instant in time) is sufficient for your use case — "2014-06-23T12:28:53" and "2014-06-23T12:28:53.000+00:00" represent the same moment if no timezone was intended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>D-DICT-1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>B.1-01_spec_example46</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
     "prefix": {
@@ -1512,135 +1585,159 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>PARSE_FAILED</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>EXCEPTION: UncheckedException: Unchecked Exception
 CAUSED_BY: UnrecognizedPropertyException: Unrecognized field "hadDictionaryMember" (class org.openprovenance.prov.core.json.serialization.SortedDocument), not marked as ignorable (23 known properties: "specializationOf", "entity", "agent", "wasEndedBy", "qualifiedHadMember", "wasAttributedTo", "activity", "alternateOf", "prefix", "wasAssociatedWith", "wasInvalidatedBy", "@id", "used", "wasDerivedFrom", "bundle", "hadMember", "wasInformedBy", "wasStartedBy", "qualifiedAlternateOf", "actedOnBehalfOf", "qualifiedSpecializationOf", "wasInfluencedBy", "wasGeneratedBy")</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All standard PROV relations (wasGeneratedBy, used, wasDerivedFrom, etc.) parse fine.
-WHAT BREAKS: The three dictionary-specific relation types from Appendix B:
-  hadDictionaryMember    (Example 46) -&gt; UnrecognizedPropertyException
-  derivedByInsertionFrom (Example 48) -&gt; UnrecognizedPropertyException
-  derivedByRemovalFrom   (Example 52) -&gt; UnrecognizedPropertyException
-The error message lists all 23 fields the deserialiser DOES recognise — dictionary types are not among them. The SortedDocument class simply has no fields for dictionary operations.
-Tests: B.1-01, B.2-01, B.3-01.</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All core PROV-JSON statement types (entity, activity, agent, all 13 relation types).
+WHAT BREAKS: All three PROV-Dictionary extension operations (hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom) are silently discarded on round-trip.
+ROOT CAUSE: SortedDocument.java lines 92-96 — the switch cases for PROV_DICTIONARY_INSERTION, PROV_DICTIONARY_REMOVAL, and PROV_DICTIONARY_MEMBERSHIP have empty break statements. The data is read but immediately thrown away.</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Spec Appendix B, Examples 46-52</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>HIGH ISSUES — COMMON PATTERNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays ["value","type"] instead of the spec-defined object format {"$":"value","type":"..."} (D2.2-1). The element order within these arrays is also non-deterministic (D2.2-8) — sometimes type-first, sometimes value-first, depending on Java hash codes. Any other spec-compliant tool reading ProvToolbox output will not recognise the typed values.</t>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>NO IN-FORMAT WORKAROUND — dictionary extensions are not supported.
+Options:
+1. MODEL AS ENTITIES: Represent dictionary operations as regular entities with custom attributes that capture the same information.
+2. PRESERVE RAW: Keep the original PROV-JSON sections in a side file and splice them back after round-trip.
+3. USE PROV-N: ProvToolbox's PROV-N format may have better dictionary support.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Inconsistent attribute handling across element types: Native string values are dropped when alone but kept in arrays (D2.2-7). prov:value partially works on entities (key survives, content lost) but is entirely dropped on agents and activities (D3.1.2-1). Multi-value xsd:string types are stripped on agents (D3.1.2-2). The behaviour depends on which element type the attribute is on and how many values it has.</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Timestamps semantically altered: All timestamps are forced into ProvToolbox's internal format — milliseconds added, microseconds truncated, and the MACHINE'S LOCAL TIMEZONE injected (D3.1.3-1). "2011-11-16T16:05:00" (no timezone) becomes "2011-11-16T16:05:00.000+01:00" (explicitly local time). Same input produces different output on different machines.</t>
+          <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays instead of the spec-defined object format with "$" and "type" properties (D2.2-1). Any other spec-compliant tool reading ProvToolbox output will not recognise the typed values. Combined with non-deterministic element order (D2.2-8), the output is both incorrect and unpredictable.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Dictionary extensions completely absent: All three PROV-Dictionary operations from Appendix B are unrecognised by the deserialiser — the SortedDocument class has no fields for them (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
+          <t>WORKAROUND AVAILABLE (D2.2-1, D2.2-8): Post-process output JSON to convert [type, value] arrays back to {"$": value, "type": type} objects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Timestamps semantically altered: All timestamps have timezone and milliseconds injected (D3.1.3-1). Adding "+00:00" changes a timezone-unspecified time to explicitly UTC — a semantic change, not just a formatting one.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>WORKAROUND AVAILABLE (D3.1.3-1): Store original timestamps and restore after round-trip, or accept normalized format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Dictionary extensions completely absent: All three PROV-Dictionary operations from Appendix B are unrecognised (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>NO WORKAROUND for dictionaries (D-DICT-1): Must model as regular entities or use PROV-N format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>MEDIUM ISSUES</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Issue ID</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Input JSON (what we sent)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Output / Error (what we got back)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Problem Description</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Spec Reference</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Workaround</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>D2.2-4</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1660,12 +1757,12 @@
 </t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1689,38 +1786,42 @@
 }</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Single values stay in place.
-WHAT BREAKS: Multi-value arrays get reordered:
-  Input:  ["alpha", "beta", "gamma"]
-  Output: ["beta", "alpha", "gamma"]
-Content survives, order does not. Array order is semantically significant in JSON, but the spec does not explicitly require preserving it.</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All values in a multi-value array survive the round-trip.
+WHAT BREAKS: The order of values within multi-value attribute arrays may change.
+ROOT CAUSE: CustomAttributeSetDeserializer.java line 37 uses HashSet for attribute storage, which has no ordering guarantee.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Accept order changes — if order matters, POST-PROCESS to re-sort arrays in a deterministic order (e.g., alphabetical by value).
+Note: The PROV-JSON spec does not explicitly require array order preservation, though JSON arrays are ordered by definition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>D3.1.1-4</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>3.1.1-03_multiple_entities</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1737,12 +1838,12 @@
 </t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1766,101 +1867,117 @@
 }</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Data within each element is complete.
-WHAT BREAKS: Element ordering within sections changes:
-  Input order:  "ex:e1", "ex:e2", "ex:e3"
-  Output order: may become "ex:e3", "ex:e1", "ex:e2"
-JSON object key order is not guaranteed by the JSON spec, so this is debatable, but many systems depend on it in practice.</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All entities and their attributes are preserved.
+WHAT BREAKS: The order of elements within sections (e.g., order of entities in the "entity" section) may change.
+ROOT CAUSE: SortedBundle.java line 14 uses HashMap for entity storage.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES — COMMON PATTERNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Ordering not preserved: Multi-value arrays get reordered (D2.2-4) — content survives but position changes. Element keys within sections are also shuffled (D3.1.1-4). JSON object key order is not guaranteed by the JSON spec, but array order is semantically significant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Accept order changes — JSON object key order is not guaranteed by RFC 8259.
+If consistent ordering matters, POST-PROCESS to sort elements alphabetically by key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Ordering not preserved: Both value order within multi-value attributes (D2.2-4) and element order within sections (D3.1.1-4) may change. While JSON object key order is not guaranteed by the JSON specification, array order is semantically significant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>WORKAROUND: Accept or post-process to re-sort in deterministic order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>LOW ISSUES</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Issue ID</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Input JSON (what we sent)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Output / Error (what we got back)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Problem Description</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Spec Reference</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Workaround</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-5</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>3.1.1-08_duplicate_entity_id</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1880,12 +1997,12 @@
 </t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1900,34 +2017,42 @@
 }</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate JSON keys in the same object — last one wins silently. This is standard JSON parser behaviour per RFC 8259, not specific to ProvToolbox.</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Standard PROV-JSON documents without duplicate keys.
+WHAT BREAKS: When the same entity ID appears twice, only the last definition survives (last-wins behavior).
+ROOT CAUSE: Standard JSON parser behavior per RFC 8259 — HashMap overwrites duplicate keys.</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>RFC 8259</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS: Validate JSON for duplicate keys before passing to ProvToolbox. Merge attributes from duplicate entries if needed.
+Note: This is standard JSON behavior, not a ProvToolbox-specific issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-7</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>3.1.1-20_prov_role</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1942,12 +2067,12 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1959,35 +2084,43 @@
 }</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: prov:role on relations (wasGeneratedBy, wasAssociatedWith, etc.) is preserved. Test 3.2.1-05 and 3.2.9-03 show prov:role surviving on relations (wrong array format, but data is there).
-WHAT BREAKS: prov:role on elements (entity, agent, activity) is dropped. PROV-DM defines prov:role for relations, not elements, so dropping it on elements is arguably correct — but it could be preserved as a generic attribute.</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: prov:role on relations (where it is defined in PROV-DM).
+WHAT BREAKS: prov:role on elements (entities, agents, activities) is dropped.
+ROOT CAUSE: HasRole.java lines 11-12 — @JsonIgnore on getRole(). prov:role is only intended for relations in PROV-DM, so it is ignored on elements.</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>PROV-DM</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>PRE-PROCESS: Rename "prov:role" to a custom attribute (e.g., "ex:role") on elements where preservation is needed.
+POST-PROCESS: Rename back.
+Note: prov:role on elements is outside PROV-DM scope, so this is arguably correct behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-8</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>3.1.1-12_empty_entity_section</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1998,12 +2131,12 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2012,35 +2145,42 @@
 }</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Sections with actual data are always present.
-WHAT BREAKS: Empty sections like "entity": {} are dropped from output entirely. No data was in them, so no data is lost. Cosmetic difference only.</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Non-empty sections are always included in output.
+WHAT BREAKS: Empty statement sections (e.g., "entity": {}) are dropped from output.
+ROOT CAUSE: @JsonInclude(JsonInclude.Include.NON_EMPTY) on JSON_Generic and related mixins.</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>Spec examples</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>Accept — empty sections carry no provenance data. No information is lost.
+If empty sections are required for schema compliance, POST-PROCESS to add them back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>D3.2.2-1</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>3.2.2-01_spec_example13</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2064,12 +2204,12 @@
 </t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2090,41 +2230,62 @@
 }</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>Property order within relation objects is changed from input. For example, "prov:entity" and "prov:activity" keys may swap positions. JSON object key order is not guaranteed. Data is intact, only structure differs.</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All relation data (participants, attributes) is preserved.
+WHAT BREAKS: Property order within relation objects changes (e.g., "prov:activity" before "prov:entity" instead of the input order).
+ROOT CAUSE: HashMap-based storage and JSON object serialization order.</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>LOW ISSUES — COMMON PATTERNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Minor structural differences: Duplicate keys use last-wins (standard JSON behaviour, D3.1.1-5). prov:role is dropped on elements but preserved on relations (D3.1.1-7). Empty sections are omitted (D3.1.1-8). Property order within relation objects changes (D3.2.2-1). No provenance data is lost in any of these cases.</t>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>Accept — JSON object key order is not guaranteed by RFC 8259. No data is lost.
+All relation properties and values are correctly preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>LOW ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Minor structural differences: These involve cosmetic changes to the JSON output — property ordering, empty section omission, duplicate key handling, and prov:role scope. No provenance data is lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>WORKAROUND: Accept these changes — they are either standard JSON behavior or carry no data loss.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A27:H27"/>
+  <mergeCells count="14">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A30:I30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -509,18 +509,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,7 +549,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Input JSON (what we sent)</t>
+          <t>Input JSON</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -558,7 +559,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Output / Error (what we got back)</t>
+          <t>Output / Error</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -573,7 +574,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Workaround</t>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
@@ -630,8 +636,7 @@
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>WHAT WORKS: Typed values like {"$":"hello","type":"xsd:string"} are accepted.
-WHAT BREAKS: Native JSON values ("hello", 42, true) used directly as attribute values are silently dropped. The entity appears in output but the attribute is gone.
-ROOT CAUSE: CustomAttributeSetDeserializer.java line 45 calls next.textValue() which returns null for non-string native JSON types.</t>
+WHAT BREAKS: Native JSON values ("hello", 42, true) used directly as attribute values are silently dropped. The entity appears in output but the attribute is gone.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -641,16 +646,14 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>PRE-PROCESS INPUT: Convert all native JSON attribute values to the explicit typed format before passing to ProvToolbox.
-Instead of:
-  "ex:name": "hello"
-Use:
-  "ex:name": [{"$": "hello", "type": "xsd:string"}]
-Instead of:
-  "ex:count": 42
-Use:
-  "ex:count": [{"$": "42", "type": "xsd:int"}]
-A simple JSON pre-processor can do this automatically.</t>
+          <t>VERIFIED: Convert native values to typed format before input.
+"ex:name": "hello" -&gt; "ex:name": [{"$": "hello", "type": "xsd:string"}]
+Tested: data survives round-trip.</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Is not supporting native JSON values (plain strings, numbers, booleans) a deliberate design choice? The spec says "MAY" — does ProvToolbox intentionally only support the typed format? If so, should it throw an error instead of silently dropping the value?</t>
         </is>
       </c>
     </row>
@@ -702,9 +705,8 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: Arrays containing only typed value objects ({"$":...,"type":...}) are processed.
-WHAT BREAKS: Mixing native JSON values (plain integers, booleans) with typed objects in the same array crashes the serialiser with UncheckedException.
-ROOT CAUSE: Same as D2.2-2 — native values in arrays create broken internal attributes that crash during serialization.</t>
+          <t>WHAT WORKS: Arrays containing only typed value objects are processed.
+WHAT BREAKS: Mixing native JSON values (plain integers, booleans) with typed objects in an array crashes the serialiser with UncheckedException.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -714,12 +716,14 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>PRE-PROCESS INPUT: Same as D2.2-2 — convert all native values in arrays to typed format.
-Instead of:
-  "ex:attr": [{"$":"a","type":"xsd:string"}, 2]
-Use:
-  "ex:attr": [{"$":"a","type":"xsd:string"}, {"$":"2","type":"xsd:int"}]
-This eliminates the crash entirely.</t>
+          <t>VERIFIED: Convert all native values in arrays to typed format.
+[{"$":"a","type":"xsd:string"}, 2] -&gt; [{"$":"a","type":"xsd:string"}, {"$":"2","type":"xsd:int"}]
+Tested: no crash, both values survive.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Even if native values are not supported, should the parser reject them with a clean error message rather than crashing with an unhandled exception? This is Spec Example 3 — is the spec example considered unsupported input?</t>
         </is>
       </c>
     </row>
@@ -777,9 +781,8 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: prov:value is parsed and stored internally — the data IS read in.
-WHAT BREAKS: prov:value is not written back out. The attribute disappears from the serialized output.
-ROOT CAUSE: JSON_Entity.java line 12 has @JsonIgnore on getValue(), telling Jackson to skip prov:value during serialization.</t>
+          <t>WHAT WORKS: prov:value is parsed and stored internally.
+WHAT BREAKS: prov:value is not written back out. The attribute disappears from the serialized output. The type name survives but the actual value data is lost.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -789,9 +792,13 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>PRE-PROCESS INPUT: Rename "prov:value" to a custom attribute (e.g., "ex:provValue") before passing to ProvToolbox.
-POST-PROCESS OUTPUT: Rename it back to "prov:value" in the output.
-Alternatively, use a different serialization format (PROV-N) for documents that need prov:value preserved.</t>
+          <t>VERIFIED: Rename "prov:value" to a custom attribute (e.g., "ex:provValue") before input. Rename back after output.
+Tested: data survives when using custom attribute name.</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>The @JsonIgnore on getValue() in JSON_Entity.java — is this intentional? Is prov:value supposed to be handled through a separate serialization path (not as a JSON attribute)? Is there a different API to access prov:value data?</t>
         </is>
       </c>
     </row>
@@ -841,9 +848,8 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: All other JSON value types (string, number, boolean, object, array) as attribute values.
-WHAT BREAKS: JSON null as an attribute value crashes the parser with NullPointerException.
-ROOT CAUSE: CustomAttributeSetDeserializer.java — null JSON nodes produce null text values, causing NPE in attribute creation.</t>
+          <t>WHAT WORKS: All other JSON value types as attribute values.
+WHAT BREAKS: JSON null as an attribute value crashes the parser with NullPointerException.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -853,9 +859,13 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>PRE-PROCESS INPUT: Validate JSON and remove or replace null attribute values before passing to ProvToolbox.
-Example: scan all attribute values and either remove null entries or replace with an empty string typed value:
-  null  →  {"$": "", "type": "xsd:string"}</t>
+          <t>VERIFIED: Remove or replace null attribute values before passing to ProvToolbox.
+Tested: replacing null with a valid value works fine.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Should the parser handle null gracefully? JSON null is a valid JSON value — should it be ignored with a warning, or is crashing the intended behavior for invalid PROV-JSON input?</t>
         </is>
       </c>
     </row>
@@ -904,9 +914,8 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: Top-level statements (entities, activities, etc.) outside bundles work fine.
-WHAT BREAKS: Every single bundle test crashes with NullPointerException. Bundles cannot be deserialized at all.
-ROOT CAUSE: SortedBundle.java line 299 — when deferredId=true, toBundle() tries to call id.getPrefix() but id is null because the bundle name was used as a map KEY but never set on the SortedBundle object during deserialization.</t>
+          <t>WHAT WORKS: Top-level statements outside bundles.
+WHAT BREAKS: Every single bundle test crashes with NullPointerException. Bundles cannot be deserialized at all in PROV-JSON format.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -916,120 +925,135 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>NO IN-FORMAT WORKAROUND — bundles are completely non-functional in PROV-JSON.
-Options:
-1. EXTRACT BUNDLES: Pre-process the JSON to extract each bundle's statements as a separate standalone document. Round-trip each individually, then manually reassemble.
-2. USE PROV-N FORMAT: Use ProvToolbox's PROV-N serializer instead, which handles bundles correctly.
-3. FLATTEN: If bundle boundaries are not critical, flatten all statements to top-level.</t>
+          <t>VERIFIED: Extract bundle contents as separate standalone documents. Round-trip individually.
+Tested: extracted bundle content produces ROUND_TRIP_IDENTICAL.
+Alternative: Use PROV-N format for bundle-containing documents.</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Is PROV-JSON bundle support known to be broken? Is it a work-in-progress? The NPE is in SortedBundle.toBundle() where this.id is null — is the bundle ID supposed to be set during deserialization through a different mechanism?</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
+          <t>CRITICAL — SUMMARY &amp; KEY QUESTIONS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Data loss on valid native JSON values: The spec explicitly allows plain JSON strings, numbers, and booleans as attribute values (MAY keyword in Section 2.2). ProvToolbox either drops them silently (D2.2-2) or crashes when they appear in mixed arrays (D2.2-3). Combined with prov:value being lost (D2.2-5), any provenance document using the simpler value formats will lose data.</t>
+          <t>Data loss on valid native JSON values: ProvToolbox either drops them silently (D2.2-2) or crashes (D2.2-3). prov:value content lost (D2.2-5).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>WORKAROUND AVAILABLE for native values (D2.2-2, D2.2-3, D2.2-5): Pre-process input JSON to convert all native values to explicit typed format, and rename prov:value to a custom attribute.</t>
+          <t>WORKAROUNDS VERIFIED for native values: Pre-process to convert all native values to typed format, rename prov:value to custom attribute.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bundles completely non-functional: Every single bundle test crashes (D3.3-1). Bundles are the primary mechanism for grouping and attributing provenance — this blocks a core use case of PROV-JSON.</t>
+          <t>Bundles completely non-functional: Every bundle test crashes (D3.3-1).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>NO WORKAROUND for bundles (D3.3-1): Must extract bundle contents into separate documents or use PROV-N format instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+          <t>WORKAROUND VERIFIED for bundles: Extract contents as separate documents, or use PROV-N format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>KEY QUESTION: Are native values (MAY in spec) intentionally unsupported? Is prov:value @JsonIgnore intentional? Are bundles a known limitation?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>HIGH ISSUES</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Issue ID</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON (what we sent)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error (what we got back)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Problem Description</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Spec Reference</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Workaround</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>D2.1-7</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>2.1-12_user_underscore_prefix</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1043,12 +1067,12 @@
 </t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1060,46 +1084,46 @@
 }</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All other user-defined namespace prefixes ("ex:", "foaf:", "custom:", etc.).
-WHAT BREAKS: Using "_" as a namespace prefix — it gets silently overwritten by ProvToolbox's internal blank node mapping to "https://openprovenance.org/blank#".
-ROOT CAUSE: SortedBundle.java lines 36-37 hardcode bnPrefix="_" and bnNS="https://openprovenance.org/blank#".</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All other user-defined namespace prefixes.
+WHAT BREAKS: Using "_" as a namespace prefix — it gets silently overwritten by ProvToolbox's internal blank node mapping.</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.1</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>PRE-PROCESS INPUT: Avoid using "_" as a namespace prefix. Rename it to something else (e.g., "underscore", "bnk", "u") in both:
-1. The "prefix" section
-2. All qualified names using that prefix
-Example:
-  "_": "http://example.org/ns/"  →  "u": "http://example.org/ns/"
-  "_:foo"  →  "u:foo"</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>VERIFIED: Rename "_" prefix to something else (e.g., "u").
+Tested: "u" prefix and "u:foo" entity survive correctly.</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Is the "_" prefix reservation for blank nodes a deliberate design choice per the PROV-DM blank node convention? The spec defines "_:" for blank node IDs — is it intentional that users cannot use "_" as a regular namespace prefix?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>D2.2-1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>2.2-01_spec_example1_typed</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1117,12 +1141,12 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1139,45 +1163,46 @@
 }</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Typed values are parsed correctly — the data survives the round-trip.
-WHAT BREAKS: The output format is wrong. Spec defines {"$":"1034","type":"xsd:positiveInteger"} but ProvToolbox outputs ["xsd:positiveInteger","1034"] — a 2-element array instead of an object.
-ROOT CAUSE: The serializer outputs typed values as flat [type, value] arrays instead of using the spec-defined object format with "$" and "type" properties.</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Typed values are parsed correctly — the data survives.
+WHAT BREAKS: Single typed values output as 2-element arrays ["type","value"] instead of {"$":"value","type":"type"} objects. Multi-value attributes correctly use objects.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2, "$" and "type" properties</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>POST-PROCESS OUTPUT: Convert 2-element arrays in attribute positions back to spec-compliant objects.
-Detection: In attribute positions, a 2-element array where one element contains ":" (type name) is a typed value.
-Conversion:
-  ["xsd:positiveInteger", "1034"]  →  {"$": "1034", "type": "xsd:positiveInteger"}
-A JSON post-processor can walk the output and fix all typed value arrays automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>POST-PROCESS OUTPUT: Convert 2-element arrays in attribute positions to {"$":value, "type":type} objects.
+Tested: data survives — both type and value are present in output.</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Is the [type, value] array format for single typed values a deliberate alternative serialization format? Is there documentation for this format? Other tools expect the spec object format — is interoperability a goal?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>D2.2-7</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>2.2-19_native_string_array</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1193,12 +1218,12 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1213,44 +1238,46 @@
 }</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Native strings survive when they appear inside arrays alongside typed values.
-WHAT BREAKS: Native strings are dropped when they are the sole attribute value (not in an array).
-ROOT CAUSE: Different code paths handle sole values vs array elements. The array path processes strings correctly, but sole native values are lost.</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Native strings survive when they appear inside arrays.
+WHAT BREAKS: Native strings are dropped when they are the sole attribute value (see D2.2-2). The behavior is inconsistent.</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>PRE-PROCESS INPUT: Same as D2.2-2 — always use typed format for all values.
-Alternatively, wrap sole native values in an array:
-  "ex:name": "hello"  →  "ex:name": ["hello"]
-But the typed format is more reliable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>VERIFIED: Use typed format for all values (same as D2.2-2).
+Tested: both original and typed format produce same output for arrays.</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Is this inconsistency (strings survive in arrays but are dropped as sole values) a known side effect of D2.2-2, or is there a different code path for sole values vs array elements?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>D2.2-8</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1270,12 +1297,12 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1299,42 +1326,46 @@
 }</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Data content survives — the type and value strings are both present.
-WHAT BREAKS: The 2-element [type, value] arrays (from D2.2-1) have non-deterministic element order. Sometimes type comes first, sometimes value comes first, depending on Java hash codes.
-ROOT CAUSE: Internal HashMap-based storage does not preserve insertion order.</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All data content survives.
+WHAT BREAKS: For single typed values output as [type, value] arrays (D2.2-1), the element order is non-deterministic — sometimes type first, sometimes value first.</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>POST-PROCESS OUTPUT: Same fix as D2.2-1 — convert arrays to objects. When converting, detect which element is the type vs. value by checking which contains ":" (qualified type names always contain a colon like "xsd:int").
-Heuristic: the element matching pattern "prefix:localPart" is the type; the other is the value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>POST-PROCESS: Same as D2.2-1 — detect type vs value by colon in qualified name pattern.
+Tested: in multi-value case, order was actually preserved. Non-determinism appears in single-value case.</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Is the element order within the [type, value] arrays expected to be stable across runs? Or is HashMap iteration order depended on?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>3.1.2-06_agent_prov_value</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1349,12 +1380,12 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1366,43 +1397,46 @@
 }</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Other agent attributes (prov:label, prov:type, prov:location, custom attributes) are preserved.
-WHAT BREAKS: prov:value on agents is read in but not written back out — same as D2.2-5 but specifically on agent elements.
-ROOT CAUSE: JSON_Entity.java @JsonIgnore on getValue() — JSON_Agent extends JSON_Entity, inheriting the ignore.</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Other agent attributes (prov:label, prov:type, prov:location, custom attributes).
+WHAT BREAKS: prov:value on agents is completely dropped — even the type name is lost (unlike entities where the type survives).</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>PROV-DM attribute definition</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Same as D2.2-5:
-PRE-PROCESS INPUT: Rename "prov:value" to a custom attribute (e.g., "ex:provValue").
-POST-PROCESS OUTPUT: Rename back to "prov:value".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>VERIFIED: Rename "prov:value" to custom attribute (e.g., "ex:provValue").
+Tested: data survives with custom attribute name.</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Same as D2.2-5 — is the @JsonIgnore on getValue() intentional? Is there a reason prov:value is treated differently from other PROV-DM attributes like prov:label and prov:type?</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-2</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>3.1.2-10_agent_multivalue_attr</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1420,12 +1454,12 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1439,42 +1473,46 @@
 }</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Single xsd:string values retain their type annotation. Non-string typed values keep their types.
-WHAT BREAKS: When an agent has 2+ xsd:string typed values for the same attribute, the type annotation is stripped — values output as bare strings instead of typed objects.
-ROOT CAUSE: CustomTypedValueSerializer.java lines 29-31 — xsd:string with a LangString value (no lang) is output as a plain JSON string, losing the type wrapper.</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Single xsd:string values, and non-string typed values like xsd:int retain type.
+WHAT BREAKS: When 2+ xsd:string typed values appear for the same attribute, the type annotation is stripped. Values survive as bare strings.</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>POST-PROCESS OUTPUT: Re-wrap bare strings inside attribute arrays with {"$": "value", "type": "xsd:string"} when the original input had typed format.
-Alternatively, PRE-PROCESS: use prov:InternationalizedString type instead of xsd:string to force type preservation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>VERIFIED: Use xsd:normalizedString instead of xsd:string to preserve type annotation.
+Tested: {"$":"developer","type":"xsd:normalizedString"} retains type in output.</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Is stripping the xsd:string type annotation intentional for readability (since plain JSON strings ARE xsd:string by default)? Is this by design to produce cleaner JSON output?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>D3.1.3-1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>3.1.3-01_spec_example9</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1495,12 +1533,12 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1516,44 +1554,46 @@
 }</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Timestamps are parsed and the date/time values are preserved.
-WHAT BREAKS: Timezone "+00:00" is injected into timezone-unspecified timestamps. Milliseconds ".000" are added. Sub-millisecond precision is truncated.
-ROOT CAUSE: CustomXMLGregorianCalendarDeserializer.java line 37 — pf.newISOTime() normalizes the calendar. CustomDateSerializer.java uses d.toString() which outputs the normalized form.</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Timestamps are parsed and date/time values preserved.
+WHAT BREAKS: Local timezone injected into timezone-unspecified timestamps. Milliseconds ".000" added. Sub-ms truncated.</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Spec Section 3.1.3, Example 9</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>PRE/POST-PROCESS:
-1. Before round-trip: extract all timestamp values from the input JSON.
-2. After round-trip: compare output timestamps with originals and restore the original format where they differ.
-Alternatively, accept the normalized format if semantic equivalence (same instant in time) is sufficient for your use case — "2014-06-23T12:28:53" and "2014-06-23T12:28:53.000+00:00" represent the same moment if no timezone was intended.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>POST-PROCESS: Store original timestamps before round-trip, restore after.
+Tested: timestamp data is present but modified. Also: the "ex:host" native string attribute is dropped (D2.2-2).</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>The ProvDeserialiser constructor accepts DateTimeOption.PRESERVE — is PRESERVE supposed to keep the original format? Is there a way to get truly unmodified timestamp strings? Is the timezone injection configurable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>D-DICT-1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>B.1-01_spec_example46</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
     "prefix": {
@@ -1585,159 +1625,152 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>PARSE_FAILED</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>EXCEPTION: UncheckedException: Unchecked Exception
 CAUSED_BY: UnrecognizedPropertyException: Unrecognized field "hadDictionaryMember" (class org.openprovenance.prov.core.json.serialization.SortedDocument), not marked as ignorable (23 known properties: "specializationOf", "entity", "agent", "wasEndedBy", "qualifiedHadMember", "wasAttributedTo", "activity", "alternateOf", "prefix", "wasAssociatedWith", "wasInvalidatedBy", "@id", "used", "wasDerivedFrom", "bundle", "hadMember", "wasInformedBy", "wasStartedBy", "qualifiedAlternateOf", "actedOnBehalfOf", "qualifiedSpecializationOf", "wasInfluencedBy", "wasGeneratedBy")</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All core PROV-JSON statement types (entity, activity, agent, all 13 relation types).
-WHAT BREAKS: All three PROV-Dictionary extension operations (hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom) are silently discarded on round-trip.
-ROOT CAUSE: SortedDocument.java lines 92-96 — the switch cases for PROV_DICTIONARY_INSERTION, PROV_DICTIONARY_REMOVAL, and PROV_DICTIONARY_MEMBERSHIP have empty break statements. The data is read but immediately thrown away.</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All core PROV-JSON statement types.
+WHAT BREAKS: hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom are all rejected as "Unrecognized field".</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Spec Appendix B, Examples 46-52</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>NO IN-FORMAT WORKAROUND — dictionary extensions are not supported.
-Options:
-1. MODEL AS ENTITIES: Represent dictionary operations as regular entities with custom attributes that capture the same information.
-2. PRESERVE RAW: Keep the original PROV-JSON sections in a side file and splice them back after round-trip.
-3. USE PROV-N: ProvToolbox's PROV-N format may have better dictionary support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>HIGH ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>VERIFIED: Model dictionary operations as regular entities with custom attributes.
+Tested: dictionary info survives as entity attributes.
+Alternative: Use PROV-N format.</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Are PROV-Dictionary extensions intentionally not supported in the JSON serializer? Is this a scope limitation or a planned feature? The PROV-DM model classes exist (SortedDocument has the switch cases) but the JSON format does not recognize the section names.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Wrong output format for typed values: The serialiser writes typed values as 2-element arrays instead of the spec-defined object format with "$" and "type" properties (D2.2-1). Any other spec-compliant tool reading ProvToolbox output will not recognise the typed values. Combined with non-deterministic element order (D2.2-8), the output is both incorrect and unpredictable.</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>WORKAROUND AVAILABLE (D2.2-1, D2.2-8): Post-process output JSON to convert [type, value] arrays back to {"$": value, "type": type} objects.</t>
+          <t>Wrong output format for typed values: Single values output as [type, value] arrays instead of {"$":...,"type":...} objects (D2.2-1). Non-deterministic order (D2.2-8).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Timestamps semantically altered: All timestamps have timezone and milliseconds injected (D3.1.3-1). Adding "+00:00" changes a timezone-unspecified time to explicitly UTC — a semantic change, not just a formatting one.</t>
+          <t>WORKAROUND VERIFIED: Post-process output to convert arrays to objects. Data is present.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>WORKAROUND AVAILABLE (D3.1.3-1): Store original timestamps and restore after round-trip, or accept normalized format.</t>
+          <t>Timestamps altered: Timezone and milliseconds injected (D3.1.3-1). Dictionary extensions rejected (D-DICT-1).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Dictionary extensions completely absent: All three PROV-Dictionary operations from Appendix B are unrecognised (D-DICT-1). Any provenance document using dictionary features will have that data silently discarded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>NO WORKAROUND for dictionaries (D-DICT-1): Must model as regular entities or use PROV-N format.</t>
+          <t>KEY QUESTION: Is the array format a deliberate alternative? Is DateTimeOption.PRESERVE working as intended? Are dictionaries planned?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM ISSUES</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON (what we sent)</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error (what we got back)</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Workaround</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>D2.2-4</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1757,12 +1790,12 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1786,42 +1819,46 @@
 }</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All values in a multi-value array survive the round-trip.
-WHAT BREAKS: The order of values within multi-value attribute arrays may change.
-ROOT CAUSE: CustomAttributeSetDeserializer.java line 37 uses HashSet for attribute storage, which has no ordering guarantee.</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All values survive.
+WHAT BREAKS: Value order within multi-value arrays may change.</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Accept order changes — if order matters, POST-PROCESS to re-sort arrays in a deterministic order (e.g., alphabetical by value).
-Note: The PROV-JSON spec does not explicitly require array order preservation, though JSON arrays are ordered by definition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Accept — or post-process to re-sort.
+Tested: in this specific test, order was actually preserved. HashSet usage means it may differ in other cases.</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>Is preserving array order a goal? The internal HashSet storage does not guarantee order — is this intentional for deduplication, or could LinkedHashSet be used instead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>D3.1.1-4</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>3.1.1-03_multiple_entities</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1838,12 +1875,12 @@
 </t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1867,117 +1904,126 @@
 }</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All entities and their attributes are preserved.
-WHAT BREAKS: The order of elements within sections (e.g., order of entities in the "entity" section) may change.
-ROOT CAUSE: SortedBundle.java line 14 uses HashMap for entity storage.</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All entities and attributes preserved.
+WHAT BREAKS: Order of elements within sections changes.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Accept order changes — JSON object key order is not guaranteed by RFC 8259.
-If consistent ordering matters, POST-PROCESS to sort elements alphabetically by key.</t>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Accept — JSON object key order is not guaranteed by RFC 8259.
+Tested: data intact, order changed.</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Is HashMap (unordered) intentional for entity/agent/activity storage? Would LinkedHashMap preserve insertion order without breaking anything?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM — SUMMARY &amp; KEY QUESTIONS</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Ordering not preserved in arrays and sections (D2.2-4, D3.1.1-4). HashSet/HashMap usage.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Ordering not preserved: Both value order within multi-value attributes (D2.2-4) and element order within sections (D3.1.1-4) may change. While JSON object key order is not guaranteed by the JSON specification, array order is semantically significant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>WORKAROUND: Accept or post-process to re-sort in deterministic order.</t>
+          <t>KEY QUESTION: Could LinkedHashSet/LinkedHashMap be used to preserve insertion order?</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>LOW ISSUES</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>LOW ISSUES</t>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON (what we sent)</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error (what we got back)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Workaround</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-5</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>3.1.1-08_duplicate_entity_id</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1997,12 +2043,12 @@
 </t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2017,42 +2063,46 @@
 }</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Standard PROV-JSON documents without duplicate keys.
-WHAT BREAKS: When the same entity ID appears twice, only the last definition survives (last-wins behavior).
-ROOT CAUSE: Standard JSON parser behavior per RFC 8259 — HashMap overwrites duplicate keys.</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Standard documents without duplicate keys.
+WHAT BREAKS: Duplicate entity IDs — last wins.</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>RFC 8259</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>PRE-PROCESS: Validate JSON for duplicate keys before passing to ProvToolbox. Merge attributes from duplicate entries if needed.
-Note: This is standard JSON behavior, not a ProvToolbox-specific issue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>Accept — standard JSON parser behavior.
+Tested: last definition survives.</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>Standard JSON behavior. Could ProvToolbox detect and warn about duplicate keys during parsing? Or is silent last-wins the preferred approach?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-7</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>3.1.1-20_prov_role</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2067,12 +2117,12 @@
 </t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2084,43 +2134,46 @@
 }</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: prov:role on relations (where it is defined in PROV-DM).
-WHAT BREAKS: prov:role on elements (entities, agents, activities) is dropped.
-ROOT CAUSE: HasRole.java lines 11-12 — @JsonIgnore on getRole(). prov:role is only intended for relations in PROV-DM, so it is ignored on elements.</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: prov:role on relations.
+WHAT BREAKS: prov:role on elements (entities, agents) is dropped.</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>PROV-DM</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>PRE-PROCESS: Rename "prov:role" to a custom attribute (e.g., "ex:role") on elements where preservation is needed.
-POST-PROCESS: Rename back.
-Note: prov:role on elements is outside PROV-DM scope, so this is arguably correct behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>VERIFIED: Rename "prov:role" to custom attribute on elements.
+Tested: "ex:role" survives on entities.</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>Is dropping prov:role on elements intentional? PROV-DM defines prov:role for relations, not elements — but should unknown prov: attributes be preserved as generic attributes rather than dropped?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-8</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>3.1.1-12_empty_entity_section</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2131,12 +2184,12 @@
 </t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2145,42 +2198,46 @@
 }</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Non-empty sections are always included in output.
-WHAT BREAKS: Empty statement sections (e.g., "entity": {}) are dropped from output.
-ROOT CAUSE: @JsonInclude(JsonInclude.Include.NON_EMPTY) on JSON_Generic and related mixins.</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Non-empty sections always included.
+WHAT BREAKS: Empty sections dropped.</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>Spec examples</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>Accept — empty sections carry no provenance data. No information is lost.
-If empty sections are required for schema compliance, POST-PROCESS to add them back.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>Accept — empty sections carry no data.
+Tested: section dropped, no data loss.</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>Is @JsonInclude(NON_EMPTY) intentional to keep output clean? Should empty sections be preserved for schema compliance?</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>D3.2.2-1</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>3.2.2-01_spec_example13</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2204,12 +2261,12 @@
 </t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2230,62 +2287,65 @@
 }</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All relation data (participants, attributes) is preserved.
-WHAT BREAKS: Property order within relation objects changes (e.g., "prov:activity" before "prov:entity" instead of the input order).
-ROOT CAUSE: HashMap-based storage and JSON object serialization order.</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All relation data preserved.
+WHAT BREAKS: Property order within relation objects changes.</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>Accept — JSON object key order is not guaranteed by RFC 8259. No data is lost.
-All relation properties and values are correctly preserved.</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>Accept — JSON key order not guaranteed.
+Tested: all properties and values intact.</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>Standard JSON behavior. Is there a @JsonPropertyOrder that could enforce consistent ordering if needed for interoperability testing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>LOW — SUMMARY &amp; KEY QUESTIONS</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>LOW ISSUES — COMMON PATTERNS &amp; WORKAROUNDS</t>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Minor structural differences: property ordering, empty sections, duplicate keys, prov:role scope. No data lost.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Minor structural differences: These involve cosmetic changes to the JSON output — property ordering, empty section omission, duplicate key handling, and prov:role scope. No provenance data is lost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>WORKAROUND: Accept these changes — they are either standard JSON behavior or carry no data loss.</t>
+          <t>KEY QUESTION: Are these design choices documented anywhere?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A30:I30"/>
+  <mergeCells count="13">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -636,12 +636,14 @@
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>WHAT WORKS: Typed values like {"$":"hello","type":"xsd:string"} are accepted.
-WHAT BREAKS: Native JSON values ("hello", 42, true) used directly as attribute values are silently dropped. The entity appears in output but the attribute is gone.</t>
+WHAT BREAKS: Native JSON values ("hello", 42, true) used directly as attribute values are silently dropped. The entity appears in output but the attribute is gone.
+IMPACT: 17 out of ~25 spec examples use native values (Ex 5,7,9,11,13,15,17,19,21,27,29,31,37,41,42,43,48). Only 6 examples use exclusively typed format. Native values are the norm in the spec, not the exception.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Spec Section 2.2, "MAY" keyword</t>
+          <t>Spec Section 2.2 "MAY" keyword.
+Affects Examples: 5 (entity), 7 (agent), 9 (activity), 11 (generation), 13 (usage), 15 (communication), 17 (start), 19 (end), 21 (invalidation), 27 (attribution), 29 (association), 31 (delegation), 37 (alternate), 41 (bundles), 42 (A.1), 43 (A.2), 48 (B.2)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -653,7 +655,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Is not supporting native JSON values (plain strings, numbers, booleans) a deliberate design choice? The spec says "MAY" — does ProvToolbox intentionally only support the typed format? If so, should it throw an error instead of silently dropping the value?</t>
+          <t>Is not supporting native JSON values (plain strings, numbers, booleans) a deliberate design choice? The spec says "MAY" — does ProvToolbox intentionally only support the typed format? If so, should it throw an error instead of silently dropping the value? 17 of ~25 spec examples use native values — is this level of incompatibility intentional?</t>
         </is>
       </c>
     </row>
@@ -706,12 +708,14 @@
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>WHAT WORKS: Arrays containing only typed value objects are processed.
-WHAT BREAKS: Mixing native JSON values (plain integers, booleans) with typed objects in an array crashes the serialiser with UncheckedException.</t>
+WHAT BREAKS: Mixing native JSON values (plain integers, booleans) with typed objects in an array crashes the serialiser with UncheckedException. This is the spec's own Example 3.
+IMPACT: Example 3 is one of only 3 examples in Section 2.2. Example 41 (bundles) also uses native numbers ("ex:version": 2). Any document following the spec's examples will crash or lose data.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Spec Section 2.2, Example 3</t>
+          <t>Spec Section 2.2, Example 3.
+Also affects: Example 41 (bundles use native numbers "ex:version": 2 and "ex:version": 1)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -723,7 +727,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Even if native values are not supported, should the parser reject them with a clean error message rather than crashing with an unhandled exception? This is Spec Example 3 — is the spec example considered unsupported input?</t>
+          <t>Even if native values are not supported, should the parser reject them with a clean error message rather than crashing with an unhandled exception? This is Spec Example 3 — 1 of only 3 examples in Section 2.2. Is the spec's own example considered unsupported input?</t>
         </is>
       </c>
     </row>
@@ -946,114 +950,107 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Data loss on valid native JSON values: ProvToolbox either drops them silently (D2.2-2) or crashes (D2.2-3). prov:value content lost (D2.2-5).</t>
+          <t>Data loss on valid native JSON values: ProvToolbox either drops them silently (D2.2-2) or crashes (D2.2-3). 17 of ~25 spec examples use native values — this affects the majority of the spec.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>WORKAROUNDS VERIFIED for native values: Pre-process to convert all native values to typed format, rename prov:value to custom attribute.</t>
+          <t>prov:value content lost (D2.2-5). Null values crash (D2.2-6). Bundles completely non-functional (D3.3-1).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bundles completely non-functional: Every bundle test crashes (D3.3-1).</t>
+          <t>WORKAROUNDS VERIFIED: Convert native values to typed format. Rename prov:value to custom attribute. Extract bundles as separate docs.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>WORKAROUND VERIFIED for bundles: Extract contents as separate documents, or use PROV-N format.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>KEY QUESTION: Are native values (MAY in spec) intentionally unsupported? Is prov:value @JsonIgnore intentional? Are bundles a known limitation?</t>
+          <t>KEY QUESTION: Are native values (MAY in spec) intentionally unsupported? 17 of ~25 spec examples would fail. Is prov:value @JsonIgnore intentional? Are bundles a known limitation?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>HIGH ISSUES</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>HIGH ISSUES</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>D2.1-7</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>2.1-12_user_underscore_prefix</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1067,12 +1064,12 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1084,46 +1081,46 @@
 }</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: All other user-defined namespace prefixes.
 WHAT BREAKS: Using "_" as a namespace prefix — it gets silently overwritten by ProvToolbox's internal blank node mapping.</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.1</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Rename "_" prefix to something else (e.g., "u").
 Tested: "u" prefix and "u:foo" entity survive correctly.</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Is the "_" prefix reservation for blank nodes a deliberate design choice per the PROV-DM blank node convention? The spec defines "_:" for blank node IDs — is it intentional that users cannot use "_" as a regular namespace prefix?</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>D2.2-1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>2.2-01_spec_example1_typed</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1141,12 +1138,12 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1163,46 +1160,46 @@
 }</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Typed values are parsed correctly — the data survives.
 WHAT BREAKS: Single typed values output as 2-element arrays ["type","value"] instead of {"$":"value","type":"type"} objects. Multi-value attributes correctly use objects.</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2, "$" and "type" properties</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS OUTPUT: Convert 2-element arrays in attribute positions to {"$":value, "type":type} objects.
 Tested: data survives — both type and value are present in output.</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Is the [type, value] array format for single typed values a deliberate alternative serialization format? Is there documentation for this format? Other tools expect the spec object format — is interoperability a goal?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>D2.2-7</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>2.2-19_native_string_array</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1218,12 +1215,12 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1238,46 +1235,46 @@
 }</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Native strings survive when they appear inside arrays.
 WHAT BREAKS: Native strings are dropped when they are the sole attribute value (see D2.2-2). The behavior is inconsistent.</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Use typed format for all values (same as D2.2-2).
 Tested: both original and typed format produce same output for arrays.</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Is this inconsistency (strings survive in arrays but are dropped as sole values) a known side effect of D2.2-2, or is there a different code path for sole values vs array elements?</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>D2.2-8</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1297,12 +1294,12 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1326,46 +1323,46 @@
 }</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: All data content survives.
 WHAT BREAKS: For single typed values output as [type, value] arrays (D2.2-1), the element order is non-deterministic — sometimes type first, sometimes value first.</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS: Same as D2.2-1 — detect type vs value by colon in qualified name pattern.
 Tested: in multi-value case, order was actually preserved. Non-determinism appears in single-value case.</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Is the element order within the [type, value] arrays expected to be stable across runs? Or is HashMap iteration order depended on?</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>3.1.2-06_agent_prov_value</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1380,12 +1377,12 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1397,46 +1394,46 @@
 }</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Other agent attributes (prov:label, prov:type, prov:location, custom attributes).
 WHAT BREAKS: prov:value on agents is completely dropped — even the type name is lost (unlike entities where the type survives).</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>PROV-DM attribute definition</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Rename "prov:value" to custom attribute (e.g., "ex:provValue").
 Tested: data survives with custom attribute name.</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Same as D2.2-5 — is the @JsonIgnore on getValue() intentional? Is there a reason prov:value is treated differently from other PROV-DM attributes like prov:label and prov:type?</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-2</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>3.1.2-10_agent_multivalue_attr</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1454,12 +1451,12 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1473,46 +1470,46 @@
 }</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Single xsd:string values, and non-string typed values like xsd:int retain type.
 WHAT BREAKS: When 2+ xsd:string typed values appear for the same attribute, the type annotation is stripped. Values survive as bare strings.</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Use xsd:normalizedString instead of xsd:string to preserve type annotation.
 Tested: {"$":"developer","type":"xsd:normalizedString"} retains type in output.</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>Is stripping the xsd:string type annotation intentional for readability (since plain JSON strings ARE xsd:string by default)? Is this by design to produce cleaner JSON output?</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>D3.1.3-1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>3.1.3-01_spec_example9</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1533,12 +1530,12 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1554,46 +1551,46 @@
 }</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Timestamps are parsed and date/time values preserved.
 WHAT BREAKS: Local timezone injected into timezone-unspecified timestamps. Milliseconds ".000" added. Sub-ms truncated.</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Spec Section 3.1.3, Example 9</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS: Store original timestamps before round-trip, restore after.
 Tested: timestamp data is present but modified. Also: the "ex:host" native string attribute is dropped (D2.2-2).</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>The ProvDeserialiser constructor accepts DateTimeOption.PRESERVE — is PRESERVE supposed to keep the original format? Is there a way to get truly unmodified timestamp strings? Is the timezone injection configurable?</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>D-DICT-1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>B.1-01_spec_example46</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
     "prefix": {
@@ -1625,152 +1622,152 @@
 </t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>PARSE_FAILED</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>EXCEPTION: UncheckedException: Unchecked Exception
 CAUSED_BY: UnrecognizedPropertyException: Unrecognized field "hadDictionaryMember" (class org.openprovenance.prov.core.json.serialization.SortedDocument), not marked as ignorable (23 known properties: "specializationOf", "entity", "agent", "wasEndedBy", "qualifiedHadMember", "wasAttributedTo", "activity", "alternateOf", "prefix", "wasAssociatedWith", "wasInvalidatedBy", "@id", "used", "wasDerivedFrom", "bundle", "hadMember", "wasInformedBy", "wasStartedBy", "qualifiedAlternateOf", "actedOnBehalfOf", "qualifiedSpecializationOf", "wasInfluencedBy", "wasGeneratedBy")</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: All core PROV-JSON statement types.
 WHAT BREAKS: hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom are all rejected as "Unrecognized field".</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Spec Appendix B, Examples 46-52</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Model dictionary operations as regular entities with custom attributes.
 Tested: dictionary info survives as entity attributes.
 Alternative: Use PROV-N format.</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>Are PROV-Dictionary extensions intentionally not supported in the JSON serializer? Is this a scope limitation or a planned feature? The PROV-DM model classes exist (SortedDocument has the switch cases) but the JSON format does not recognize the section names.</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Wrong output format for typed values: Single values output as [type, value] arrays instead of {"$":...,"type":...} objects (D2.2-1). Non-deterministic order (D2.2-8).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Wrong output format for typed values: Single values output as [type, value] arrays instead of {"$":...,"type":...} objects (D2.2-1). Non-deterministic order (D2.2-8).</t>
+          <t>WORKAROUND VERIFIED: Post-process output to convert arrays to objects. Data is present.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>WORKAROUND VERIFIED: Post-process output to convert arrays to objects. Data is present.</t>
+          <t>Timestamps altered: Timezone and milliseconds injected (D3.1.3-1). Dictionary extensions rejected (D-DICT-1).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Timestamps altered: Timezone and milliseconds injected (D3.1.3-1). Dictionary extensions rejected (D-DICT-1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
           <t>KEY QUESTION: Is the array format a deliberate alternative? Is DateTimeOption.PRESERVE working as intended? Are dictionaries planned?</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM ISSUES</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>D2.2-4</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1790,12 +1787,12 @@
 </t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1819,46 +1816,46 @@
 }</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All values survive.
 WHAT BREAKS: Value order within multi-value arrays may change.</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Accept — or post-process to re-sort.
 Tested: in this specific test, order was actually preserved. HashSet usage means it may differ in other cases.</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Is preserving array order a goal? The internal HashSet storage does not guarantee order — is this intentional for deduplication, or could LinkedHashSet be used instead?</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>D3.1.1-4</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>3.1.1-03_multiple_entities</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1875,12 +1872,12 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1904,126 +1901,126 @@
 }</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All entities and attributes preserved.
 WHAT BREAKS: Order of elements within sections changes.</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Accept — JSON object key order is not guaranteed by RFC 8259.
 Tested: data intact, order changed.</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Is HashMap (unordered) intentional for entity/agent/activity storage? Would LinkedHashMap preserve insertion order without breaking anything?</t>
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Ordering not preserved in arrays and sections (D2.2-4, D3.1.1-4). HashSet/HashMap usage.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Ordering not preserved in arrays and sections (D2.2-4, D3.1.1-4). HashSet/HashMap usage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
           <t>KEY QUESTION: Could LinkedHashSet/LinkedHashMap be used to preserve insertion order?</t>
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>LOW ISSUES</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>LOW ISSUES</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-5</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>3.1.1-08_duplicate_entity_id</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2043,12 +2040,12 @@
 </t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2063,46 +2060,46 @@
 }</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: Standard documents without duplicate keys.
 WHAT BREAKS: Duplicate entity IDs — last wins.</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>RFC 8259</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>Accept — standard JSON parser behavior.
 Tested: last definition survives.</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>Standard JSON behavior. Could ProvToolbox detect and warn about duplicate keys during parsing? Or is silent last-wins the preferred approach?</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-7</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>3.1.1-20_prov_role</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2117,12 +2114,12 @@
 </t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2134,46 +2131,46 @@
 }</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: prov:role on relations.
 WHAT BREAKS: prov:role on elements (entities, agents) is dropped.</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>PROV-DM</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>VERIFIED: Rename "prov:role" to custom attribute on elements.
 Tested: "ex:role" survives on entities.</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>Is dropping prov:role on elements intentional? PROV-DM defines prov:role for relations, not elements — but should unknown prov: attributes be preserved as generic attributes rather than dropped?</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-8</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>3.1.1-12_empty_entity_section</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2184,12 +2181,12 @@
 </t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2198,46 +2195,46 @@
 }</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: Non-empty sections always included.
 WHAT BREAKS: Empty sections dropped.</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>Spec examples</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>Accept — empty sections carry no data.
 Tested: section dropped, no data loss.</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>Is @JsonInclude(NON_EMPTY) intentional to keep output clean? Should empty sections be preserved for schema compliance?</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>D3.2.2-1</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>3.2.2-01_spec_example13</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2261,12 +2258,12 @@
 </t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2287,63 +2284,62 @@
 }</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: All relation data preserved.
 WHAT BREAKS: Property order within relation objects changes.</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>Accept — JSON key order not guaranteed.
 Tested: all properties and values intact.</t>
         </is>
       </c>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>Standard JSON behavior. Is there a @JsonPropertyOrder that could enforce consistent ordering if needed for interoperability testing?</t>
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>LOW — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>LOW — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Minor structural differences: property ordering, empty sections, duplicate keys, prov:role scope. No data lost.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Minor structural differences: property ordering, empty sections, duplicate keys, prov:role scope. No data lost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
           <t>KEY QUESTION: Are these design choices documented anywhere?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A40:J40"/>
+  <mergeCells count="12">
+    <mergeCell ref="A27:J27"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A49:J49"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -785,13 +785,16 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>WHAT WORKS: prov:value is parsed and stored internally.
-WHAT BREAKS: prov:value is not written back out. The attribute disappears from the serialized output. The type name survives but the actual value data is lost.</t>
+          <t>WHAT WORKS: prov:value is parsed and stored internally. prov:type and prov:label serialize fine.
+WHAT BREAKS: prov:value is not written back out. The type name "xsd:int" survives but the actual value "42" is lost.
+NOTE: No PROV-JSON spec example uses prov:value (prov:type is used in 15+ examples). But prov:type, prov:label, and prov:value are all standard PROV attributes — only prov:value has @JsonIgnore.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>PROV-DM attribute definition</t>
+          <t>No PROV-JSON spec example uses prov:value.
+prov:type (handled correctly) appears in Examples 5,7,9,11,15,17,19,25,27,29,31,37,41,42,43,45,47,51.
+prov:value is a standard attribute like prov:type — but not demonstrated in the JSON spec.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -802,7 +805,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>The @JsonIgnore on getValue() in JSON_Entity.java — is this intentional? Is prov:value supposed to be handled through a separate serialization path (not as a JSON attribute)? Is there a different API to access prov:value data?</t>
+          <t>The @JsonIgnore on getValue() in JSON_Entity.java — is this intentional? prov:type and prov:label serialize fine — why is prov:value treated differently? Is it handled through a separate serialization path?</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1400,14 @@
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Other agent attributes (prov:label, prov:type, prov:location, custom attributes).
-WHAT BREAKS: prov:value on agents is completely dropped — even the type name is lost (unlike entities where the type survives).</t>
+WHAT BREAKS: prov:value on agents is completely dropped — even the type name is lost (unlike entities where the type survives).
+Same root cause as D2.2-5. No PROV-JSON spec example uses prov:value.</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PROV-DM attribute definition</t>
+          <t>No PROV-JSON spec example uses prov:value.
+Same root cause as D2.2-5 — @JsonIgnore on getValue() in JSON_Agent.java.</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -1413,7 +1418,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Same as D2.2-5 — is the @JsonIgnore on getValue() intentional? Is there a reason prov:value is treated differently from other PROV-DM attributes like prov:label and prov:type?</t>
+          <t>Same as D2.2-5 — prov:type and prov:label serialize fine on agents. Why does prov:value have @JsonIgnore? Is it handled through a separate path?</t>
         </is>
       </c>
     </row>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -1040,7 +1040,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>D2.1-7</t>
+          <t>D2.2-1</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1050,80 +1050,10 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>2.1-12_user_underscore_prefix</t>
+          <t>2.2-01_spec_example1_typed</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "prefix": {
-    "ex": "http://example.org/",
-    "_": "http://example.org/my-blanks/"
-  },
-  "entity": {
-    "ex:e1": {}
-  }
-}
-</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>ROUND_TRIP_CHANGED</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>{
-"prefix" : {
-"ex" : "http://example.org/"
-},
-"entity" : {
-"ex:e1" : { }
-}
-}</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All other user-defined namespace prefixes.
-WHAT BREAKS: Using "_" as a namespace prefix — it gets silently overwritten by ProvToolbox's internal blank node mapping.</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Spec Section 2.1</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED: Rename "_" prefix to something else (e.g., "u").
-Tested: "u" prefix and "u:foo" entity survive correctly.</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>Is the "_" prefix reservation for blank nodes a deliberate design choice per the PROV-DM blank node convention? The spec defines "_:" for blank node IDs — is it intentional that users cannot use "_" as a regular namespace prefix?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>D2.2-1</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>2.2-01_spec_example1_typed</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1141,12 +1071,12 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1163,46 +1093,46 @@
 }</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Typed values are parsed correctly — the data survives.
 WHAT BREAKS: Single typed values output as 2-element arrays ["type","value"] instead of {"$":"value","type":"type"} objects. Multi-value attributes correctly use objects.</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2, "$" and "type" properties</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS OUTPUT: Convert 2-element arrays in attribute positions to {"$":value, "type":type} objects.
 Tested: data survives — both type and value are present in output.</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Is the [type, value] array format for single typed values a deliberate alternative serialization format? Is there documentation for this format? Other tools expect the spec object format — is interoperability a goal?</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>D2.2-7</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>2.2-19_native_string_array</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1218,12 +1148,12 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1238,46 +1168,46 @@
 }</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Native strings survive when they appear inside arrays.
 WHAT BREAKS: Native strings are dropped when they are the sole attribute value (see D2.2-2). The behavior is inconsistent.</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Use typed format for all values (same as D2.2-2).
 Tested: both original and typed format produce same output for arrays.</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Is this inconsistency (strings survive in arrays but are dropped as sole values) a known side effect of D2.2-2, or is there a different code path for sole values vs array elements?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>D2.2-8</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1297,12 +1227,12 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1326,46 +1256,46 @@
 }</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: All data content survives.
 WHAT BREAKS: For single typed values output as [type, value] arrays (D2.2-1), the element order is non-deterministic — sometimes type first, sometimes value first.</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS: Same as D2.2-1 — detect type vs value by colon in qualified name pattern.
 Tested: in multi-value case, order was actually preserved. Non-determinism appears in single-value case.</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Is the element order within the [type, value] arrays expected to be stable across runs? Or is HashMap iteration order depended on?</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>3.1.2-06_agent_prov_value</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1380,12 +1310,12 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1397,48 +1327,48 @@
 }</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Other agent attributes (prov:label, prov:type, prov:location, custom attributes).
 WHAT BREAKS: prov:value on agents is completely dropped — even the type name is lost (unlike entities where the type survives).
 Same root cause as D2.2-5. No PROV-JSON spec example uses prov:value.</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>No PROV-JSON spec example uses prov:value.
 Same root cause as D2.2-5 — @JsonIgnore on getValue() in JSON_Agent.java.</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Rename "prov:value" to custom attribute (e.g., "ex:provValue").
 Tested: data survives with custom attribute name.</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Same as D2.2-5 — prov:type and prov:label serialize fine on agents. Why does prov:value have @JsonIgnore? Is it handled through a separate path?</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>D3.1.2-2</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>3.1.2-10_agent_multivalue_attr</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1456,12 +1386,12 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1475,46 +1405,46 @@
 }</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Single xsd:string values, and non-string typed values like xsd:int retain type.
 WHAT BREAKS: When 2+ xsd:string typed values appear for the same attribute, the type annotation is stripped. Values survive as bare strings.</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Use xsd:normalizedString instead of xsd:string to preserve type annotation.
 Tested: {"$":"developer","type":"xsd:normalizedString"} retains type in output.</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Is stripping the xsd:string type annotation intentional for readability (since plain JSON strings ARE xsd:string by default)? Is this by design to produce cleaner JSON output?</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>D3.1.3-1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>3.1.3-01_spec_example9</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1535,12 +1465,12 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1556,46 +1486,46 @@
 }</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Timestamps are parsed and date/time values preserved.
 WHAT BREAKS: Local timezone injected into timezone-unspecified timestamps. Milliseconds ".000" added. Sub-ms truncated.</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Spec Section 3.1.3, Example 9</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS: Store original timestamps before round-trip, restore after.
 Tested: timestamp data is present but modified. Also: the "ex:host" native string attribute is dropped (D2.2-2).</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>The ProvDeserialiser constructor accepts DateTimeOption.PRESERVE — is PRESERVE supposed to keep the original format? Is there a way to get truly unmodified timestamp strings? Is the timezone injection configurable?</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>D-DICT-1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>B.1-01_spec_example46</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
     "prefix": {
@@ -1627,152 +1557,152 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>PARSE_FAILED</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>EXCEPTION: UncheckedException: Unchecked Exception
 CAUSED_BY: UnrecognizedPropertyException: Unrecognized field "hadDictionaryMember" (class org.openprovenance.prov.core.json.serialization.SortedDocument), not marked as ignorable (23 known properties: "specializationOf", "entity", "agent", "wasEndedBy", "qualifiedHadMember", "wasAttributedTo", "activity", "alternateOf", "prefix", "wasAssociatedWith", "wasInvalidatedBy", "@id", "used", "wasDerivedFrom", "bundle", "hadMember", "wasInformedBy", "wasStartedBy", "qualifiedAlternateOf", "actedOnBehalfOf", "qualifiedSpecializationOf", "wasInfluencedBy", "wasGeneratedBy")</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: All core PROV-JSON statement types.
 WHAT BREAKS: hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom are all rejected as "Unrecognized field".</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Spec Appendix B, Examples 46-52</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>VERIFIED: Model dictionary operations as regular entities with custom attributes.
 Tested: dictionary info survives as entity attributes.
 Alternative: Use PROV-N format.</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>Are PROV-Dictionary extensions intentionally not supported in the JSON serializer? Is this a scope limitation or a planned feature? The PROV-DM model classes exist (SortedDocument has the switch cases) but the JSON format does not recognize the section names.</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Wrong output format for typed values: Single values output as [type, value] arrays instead of {"$":...,"type":...} objects (D2.2-1). Non-deterministic order (D2.2-8).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Wrong output format for typed values: Single values output as [type, value] arrays instead of {"$":...,"type":...} objects (D2.2-1). Non-deterministic order (D2.2-8).</t>
+          <t>WORKAROUND VERIFIED: Post-process output to convert arrays to objects. Data is present.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>WORKAROUND VERIFIED: Post-process output to convert arrays to objects. Data is present.</t>
+          <t>Timestamps altered: Timezone and milliseconds injected (D3.1.3-1). Dictionary extensions rejected (D-DICT-1).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Timestamps altered: Timezone and milliseconds injected (D3.1.3-1). Dictionary extensions rejected (D-DICT-1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
           <t>KEY QUESTION: Is the array format a deliberate alternative? Is DateTimeOption.PRESERVE working as intended? Are dictionaries planned?</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM ISSUES</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>D2.2-4</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1792,12 +1722,12 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1821,46 +1751,46 @@
 }</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All values survive.
 WHAT BREAKS: Value order within multi-value arrays may change.</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Accept — or post-process to re-sort.
 Tested: in this specific test, order was actually preserved. HashSet usage means it may differ in other cases.</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Is preserving array order a goal? The internal HashSet storage does not guarantee order — is this intentional for deduplication, or could LinkedHashSet be used instead?</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>D3.1.1-4</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>3.1.1-03_multiple_entities</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1877,12 +1807,12 @@
 </t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1906,106 +1836,178 @@
 }</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All entities and attributes preserved.
 WHAT BREAKS: Order of elements within sections changes.</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Accept — JSON object key order is not guaranteed by RFC 8259.
 Tested: data intact, order changed.</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Is HashMap (unordered) intentional for entity/agent/activity storage? Would LinkedHashMap preserve insertion order without breaking anything?</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Ordering not preserved in arrays and sections (D2.2-4, D3.1.1-4). HashSet/HashMap usage.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Ordering not preserved in arrays and sections (D2.2-4, D3.1.1-4). HashSet/HashMap usage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
           <t>KEY QUESTION: Could LinkedHashSet/LinkedHashMap be used to preserve insertion order?</t>
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>LOW ISSUES</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>LOW ISSUES</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>D2.1-7</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>2.1-12_user_underscore_prefix</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "prefix": {
+    "ex": "http://example.org/",
+    "_": "http://example.org/my-blanks/"
+  },
+  "entity": {
+    "ex:e1": {}
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"entity" : {
+"ex:e1" : { }
+}
+}</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All other user-defined namespace prefixes.
+WHAT BREAKS: Using "_" as a namespace prefix — it gets silently overwritten by ProvToolbox's internal blank node mapping.
+Likely a design choice: Spec Section 2.1 reserves "_:" for blank node IDs (e.g. _:A1). ProvToolbox extends this by reserving the "_" prefix entirely. This is consistent with Turtle/RDF conventions.</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Spec Section 2.1: "blank node identifiers MUST be created following the nodeID production in Turtle (e.g. _:A1)".
+No spec example uses "_" as a user-defined prefix. Reserving "_" is consistent with RDF blank node conventions.</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>VERIFIED: Rename "_" prefix to something else (e.g., "u").
+Tested: "u" prefix and "u:foo" entity survive correctly.</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Likely a design choice. The spec reserves "_:" for blank nodes — is extending that to the entire "_" prefix intentional? Should there be a warning when a user tries to use "_" as a namespace prefix?</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2337,12 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A37:J37"/>
     <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A28:J28"/>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1096,12 +1096,15 @@
       <c r="G17" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Typed values are parsed correctly — the data survives.
-WHAT BREAKS: Single typed values output as 2-element arrays ["type","value"] instead of {"$":"value","type":"type"} objects. Multi-value attributes correctly use objects.</t>
+WHAT BREAKS: Single typed values output as 2-element arrays ["type","value"] instead of {"$":"value","type":"type"} objects. Multi-value attributes correctly use objects.
+CLEAR SPEC VIOLATION: Spec defines ONE format — {"$": value, "type": type}. The array format has zero basis in the spec.</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Spec Section 2.2, "$" and "type" properties</t>
+          <t>Spec Section 2.2, Example 1.
+Spec text: "The value of a literal is stored in the object's special property $... the data type in the type property."
+No alternative format defined anywhere in the spec.</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -1112,27 +1115,199 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>Is the [type, value] array format for single typed values a deliberate alternative serialization format? Is there documentation for this format? Other tools expect the spec object format — is interoperability a goal?</t>
+          <t>Is the [type, value] array format a deliberate alternative? The spec defines only the {"$","type"} object format (Example 1). Is there documentation for this alternative? Other tools expect the spec format.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>D3.1.3-1</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>3.1.3-01_spec_example9</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "prefix": {
+    "ex": "http://example.org/"
+  },
+  "activity": {
+    "ex:a1": {
+      "prov:startTime": "2011-11-16T16:05:00",
+      "prov:endTime": "2011-11-16T16:06:00",
+      "ex:host": "server.example.org",
+      "prov:type": {
+        "$": "ex:edit",
+        "type": "prov:QualifiedName"
+      }
+    }
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"ex" : "http://example.org/"
+},
+"activity" : {
+"ex:a1" : {
+"prov:startTime" : "2011-11-16T16:05:00.000+01:00",
+"prov:endTime" : "2011-11-16T16:06:00.000+01:00",
+"prov:type" : [ "prov:QualifiedName", "ex:edit" ]
+}
+}
+}</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: Timestamps are parsed and date/time values preserved.
+WHAT BREAKS: Local timezone injected into timezone-unspecified timestamps. Milliseconds ".000" added.
+SEMANTIC CHANGE: In xsd:dateTime, "2011-11-16T16:05:00" (no timezone) and "2011-11-16T16:05:00.000+01:00" (with timezone) are DIFFERENT values. No timezone means "unspecified," not "local time." Injecting timezone changes the meaning of the data.</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Spec Section 3.1.3, Example 9: timestamps shown as "2011-11-16T16:05:00" (no timezone, no milliseconds).
+Spec: "values of startTime and endTime MUST conform to xsd:dateTime."
+Every spec timestamp example (9,11,13,17,21,41) has no timezone.
+In xsd:dateTime, absent timezone != UTC != local — they are semantically different.</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>POST-PROCESS: Store original timestamps before round-trip, restore after.
+Tested: timestamp data is present but modified. Also: the "ex:host" native string attribute is dropped (D2.2-2).</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Injecting timezone changes the semantic meaning of the timestamp. Every spec example has no timezone. Is DateTimeOption.PRESERVE supposed to keep the original format? Is timezone injection configurable?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>CLEAR SPEC VIOLATION: Typed values output as [type, value] arrays instead of {"$","type"} objects (D2.2-1). Spec defines ONE format in Example 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>SEMANTIC CHANGE: Timezone injected into timestamps (D3.1.3-1). In xsd:dateTime, absent timezone != local time. Every spec example (9,11,13,17,21,41) has no timezone. Injecting one changes the meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>WORKAROUNDS: Post-process arrays to objects (D2.2-1). Store/restore original timestamps (D3.1.3-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM ISSUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
           <t>D2.2-7</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>2.2-19_native_string_array</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1148,12 +1323,12 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1168,46 +1343,50 @@
 }</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: Native strings survive when they appear inside arrays.
-WHAT BREAKS: Native strings are dropped when they are the sole attribute value (see D2.2-2). The behavior is inconsistent.</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Spec Section 2.2</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
+WHAT BREAKS: Native strings are dropped when they are the sole attribute value (see D2.2-2). The behavior is inconsistent.
+Side effect of D2.2-2. The spec MAY clause makes no distinction between single and array contexts — applies equally to both.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Spec Section 2.2 MAY clause.
+Examples 5, 41 use native values as single values.
+Example 3 uses native values in arrays.
+Spec treats both contexts the same.</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>VERIFIED: Use typed format for all values (same as D2.2-2).
 Tested: both original and typed format produce same output for arrays.</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Is this inconsistency (strings survive in arrays but are dropped as sole values) a known side effect of D2.2-2, or is there a different code path for sole values vs array elements?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Side effect of D2.2-2. Is the different behavior between single values and arrays a known inconsistency?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>D2.2-8</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1227,12 +1406,12 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1256,46 +1435,49 @@
 }</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All data content survives.
-WHAT BREAKS: For single typed values output as [type, value] arrays (D2.2-1), the element order is non-deterministic — sometimes type first, sometimes value first.</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Spec Section 2.2</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
+WHAT BREAKS: For single typed values output as [type, value] arrays (D2.2-1), the element order is non-deterministic.
+Secondary to D2.2-1. The spec defines objects (where order doesn't matter), not arrays. This issue only exists because of the wrong output format.</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Spec Section 2.2, Example 1.
+The spec format is {"$","type"} objects where property order has no meaning (RFC 8259).
+This issue is a downstream consequence of D2.2-1 using the wrong format.</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>POST-PROCESS: Same as D2.2-1 — detect type vs value by colon in qualified name pattern.
 Tested: in multi-value case, order was actually preserved. Non-determinism appears in single-value case.</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>Is the element order within the [type, value] arrays expected to be stable across runs? Or is HashMap iteration order depended on?</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Secondary to D2.2-1. If the output used the spec object format, this issue would not exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>D3.1.2-1</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>3.1.2-06_agent_prov_value</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1310,12 +1492,12 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1327,48 +1509,49 @@
 }</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: Other agent attributes (prov:label, prov:type, prov:location, custom attributes).
-WHAT BREAKS: prov:value on agents is completely dropped — even the type name is lost (unlike entities where the type survives).
-Same root cause as D2.2-5. No PROV-JSON spec example uses prov:value.</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>No PROV-JSON spec example uses prov:value.
-Same root cause as D2.2-5 — @JsonIgnore on getValue() in JSON_Agent.java.</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
+WHAT BREAKS: prov:value on agents is completely dropped.
+No PROV-JSON spec example uses prov:value on agents or anything else. Example 7 (agent) shows prov:type but not prov:value. Same root cause as D2.2-5.</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Section 3.1.2, Example 7 — agent example uses prov:type but NOT prov:value.
+No PROV-JSON spec example uses prov:value anywhere.
+Spec does not exclude any attributes — but does not demonstrate this one.</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>VERIFIED: Rename "prov:value" to custom attribute (e.g., "ex:provValue").
 Tested: data survives with custom attribute name.</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Same as D2.2-5 — prov:type and prov:label serialize fine on agents. Why does prov:value have @JsonIgnore? Is it handled through a separate path?</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Same as D2.2-5 — prov:type and prov:label serialize fine. Why does prov:value have @JsonIgnore? No spec example uses it — is this a deliberate omission?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>D3.1.2-2</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>3.1.2-10_agent_multivalue_attr</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1386,12 +1569,12 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1405,127 +1588,50 @@
 }</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: Single xsd:string values, and non-string typed values like xsd:int retain type.
-WHAT BREAKS: When 2+ xsd:string typed values appear for the same attribute, the type annotation is stripped. Values survive as bare strings.</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Spec Section 2.2</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
+WHAT BREAKS: When 2+ xsd:string typed values appear for the same attribute, the type annotation is stripped.
+Spec says MAY: "xsd:string values MAY be represented using native JSON strings." Stripping is PERMITTED. Only the inconsistency (strips on multi but not single) is the issue.</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Spec Section 2.2 MAY clause.
+Stripping xsd:string type is permitted by spec.
+No spec example shows multiple xsd:string typed values on one attribute.
+Both formats (typed and native) are valid output per the spec.</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>VERIFIED: Use xsd:normalizedString instead of xsd:string to preserve type annotation.
 Tested: {"$":"developer","type":"xsd:normalizedString"} retains type in output.</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Is stripping the xsd:string type annotation intentional for readability (since plain JSON strings ARE xsd:string by default)? Is this by design to produce cleaner JSON output?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>D3.1.3-1</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>3.1.3-01_spec_example9</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "prefix": {
-    "ex": "http://example.org/"
-  },
-  "activity": {
-    "ex:a1": {
-      "prov:startTime": "2011-11-16T16:05:00",
-      "prov:endTime": "2011-11-16T16:06:00",
-      "ex:host": "server.example.org",
-      "prov:type": {
-        "$": "ex:edit",
-        "type": "prov:QualifiedName"
-      }
-    }
-  }
-}
-</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>ROUND_TRIP_CHANGED</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>{
-"prefix" : {
-"ex" : "http://example.org/"
-},
-"activity" : {
-"ex:a1" : {
-"prov:startTime" : "2011-11-16T16:05:00.000+01:00",
-"prov:endTime" : "2011-11-16T16:06:00.000+01:00",
-"prov:type" : [ "prov:QualifiedName", "ex:edit" ]
-}
-}
-}</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: Timestamps are parsed and date/time values preserved.
-WHAT BREAKS: Local timezone injected into timezone-unspecified timestamps. Milliseconds ".000" added. Sub-ms truncated.</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Spec Section 3.1.3, Example 9</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>POST-PROCESS: Store original timestamps before round-trip, restore after.
-Tested: timestamp data is present but modified. Also: the "ex:host" native string attribute is dropped (D2.2-2).</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>The ProvDeserialiser constructor accepts DateTimeOption.PRESERVE — is PRESERVE supposed to keep the original format? Is there a way to get truly unmodified timestamp strings? Is the timezone injection configurable?</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Spec permits stripping xsd:string type (MAY clause). Is the inconsistency (strips on multi-value but not single) intentional?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>D-DICT-1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>B.1-01_spec_example46</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
     "prefix": {
@@ -1557,152 +1663,62 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>PARSE_FAILED</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>EXCEPTION: UncheckedException: Unchecked Exception
 CAUSED_BY: UnrecognizedPropertyException: Unrecognized field "hadDictionaryMember" (class org.openprovenance.prov.core.json.serialization.SortedDocument), not marked as ignorable (23 known properties: "specializationOf", "entity", "agent", "wasEndedBy", "qualifiedHadMember", "wasAttributedTo", "activity", "alternateOf", "prefix", "wasAssociatedWith", "wasInvalidatedBy", "@id", "used", "wasDerivedFrom", "bundle", "hadMember", "wasInformedBy", "wasStartedBy", "qualifiedAlternateOf", "actedOnBehalfOf", "qualifiedSpecializationOf", "wasInfluencedBy", "wasGeneratedBy")</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All core PROV-JSON statement types.
-WHAT BREAKS: hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom are all rejected as "Unrecognized field".</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Spec Appendix B, Examples 46-52</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
+WHAT BREAKS: hadDictionaryMember, derivedByInsertionFrom, derivedByRemovalFrom are all rejected as "Unrecognized field".
+OPTIONAL EXTENSION: Appendix B is technically normative but PROV-Dictionary is a W3C Note, not a Recommendation. It defines HOW to serialize dictionaries, not that tools MUST support them.</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Spec Appendix B, Examples 46-52.
+Appendix B is normative (not marked informative).
+But PROV-Dictionary is a W3C Note, not a Recommendation.
+Spec defines the serialization format but does not require implementations to support dictionary constructs.</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>VERIFIED: Model dictionary operations as regular entities with custom attributes.
 Tested: dictionary info survives as entity attributes.
 Alternative: Use PROV-N format.</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Are PROV-Dictionary extensions intentionally not supported in the JSON serializer? Is this a scope limitation or a planned feature? The PROV-DM model classes exist (SortedDocument has the switch cases) but the JSON format does not recognize the section names.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Wrong output format for typed values: Single values output as [type, value] arrays instead of {"$":...,"type":...} objects (D2.2-1). Non-deterministic order (D2.2-8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>WORKAROUND VERIFIED: Post-process output to convert arrays to objects. Data is present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Timestamps altered: Timezone and milliseconds injected (D3.1.3-1). Dictionary extensions rejected (D-DICT-1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>KEY QUESTION: Is the array format a deliberate alternative? Is DateTimeOption.PRESERVE working as intended? Are dictionaries planned?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES</t>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>PROV-Dictionary is a W3C Note (optional). Is dictionary support planned, or is this an intentional scope limitation?</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>D2.2-4</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>2.2-10_array_typed_values</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1722,12 +1738,12 @@
 </t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1751,46 +1767,46 @@
 }</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All values survive.
 WHAT BREAKS: Value order within multi-value arrays may change.</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>Spec Section 2.2</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Accept — or post-process to re-sort.
 Tested: in this specific test, order was actually preserved. HashSet usage means it may differ in other cases.</t>
         </is>
       </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Is preserving array order a goal? The internal HashSet storage does not guarantee order — is this intentional for deduplication, or could LinkedHashSet be used instead?</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>D3.1.1-4</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>3.1.1-03_multiple_entities</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1807,12 +1823,12 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1836,33 +1852,40 @@
 }</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>WHAT WORKS: All entities and attributes preserved.
 WHAT BREAKS: Order of elements within sections changes.</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Accept — JSON object key order is not guaranteed by RFC 8259.
 Tested: data intact, order changed.</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Is HashMap (unordered) intentional for entity/agent/activity storage? Would LinkedHashMap preserve insertion order without breaking anything?</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Side effects and optional extensions: D2.2-7 (inconsistency from D2.2-2), D2.2-8 (downstream of D2.2-1), D3.1.2-1 (prov:value — no spec example), D3.1.2-2 (xsd:string stripping — spec says MAY), D-DICT-1 (W3C Note, optional).</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1899,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>KEY QUESTION: Could LinkedHashSet/LinkedHashMap be used to preserve insertion order?</t>
+          <t>KEY QUESTION: Are these intentional design choices or side effects of the CRITICAL/HIGH issues?</t>
         </is>
       </c>
     </row>
@@ -2324,28 +2347,36 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Minor structural differences: property ordering, empty sections, duplicate keys, prov:role scope. No data lost.</t>
+          <t>Minor structural differences: property ordering, empty sections, duplicate keys, prov:role scope, underscore prefix. No data lost.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
+          <t>D2.1-7 ("_" prefix): Spec reserves "_:" for blank nodes. ProvToolbox extending this to the prefix is consistent with RDF conventions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
           <t>KEY QUESTION: Are these design choices documented anywhere?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A21:J21"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A29:J29"/>
     <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A51:J51"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A28:J28"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A11:J11"/>

--- a/issues_report.xlsx
+++ b/issues_report.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>D2.2-5</t>
+          <t>D3.3-1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -744,155 +744,10 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2.2-15_prov_value_typed</t>
+          <t>3.3-01_minimal_bundle</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "prefix": {
-    "default": "http://example.org/",
-    "ex": "http://example.org/"
-  },
-  "entity": {
-    "e1": {
-      "prov:value": {"$": "42", "type": "xsd:int"}
-    }
-  }
-}
-</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>ROUND_TRIP_CHANGED</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>{
-"prefix" : {
-"default" : "http://example.org/",
-"ex" : "http://example.org/"
-},
-"entity" : {
-"e1" : {
-"prov:value" : [ "xsd:int" ]
-}
-}
-}</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: prov:value is parsed and stored internally. prov:type and prov:label serialize fine.
-WHAT BREAKS: prov:value is not written back out. The type name "xsd:int" survives but the actual value "42" is lost.
-NOTE: No PROV-JSON spec example uses prov:value (prov:type is used in 15+ examples). But prov:type, prov:label, and prov:value are all standard PROV attributes — only prov:value has @JsonIgnore.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>No PROV-JSON spec example uses prov:value.
-prov:type (handled correctly) appears in Examples 5,7,9,11,15,17,19,25,27,29,31,37,41,42,43,45,47,51.
-prov:value is a standard attribute like prov:type — but not demonstrated in the JSON spec.</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>VERIFIED: Rename "prov:value" to a custom attribute (e.g., "ex:provValue") before input. Rename back after output.
-Tested: data survives when using custom attribute name.</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>The @JsonIgnore on getValue() in JSON_Entity.java — is this intentional? prov:type and prov:label serialize fine — why is prov:value treated differently? Is it handled through a separate serialization path?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>D2.2-6</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2.2-21_json_null_value</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{
-  "prefix": {
-    "default": "http://example.org/",
-    "ex": "http://example.org/"
-  },
-  "entity": {
-    "e1": {
-      "ex:missing": null
-    }
-  }
-}
-</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>PARSE_FAILED</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>EXCEPTION: UncheckedException: Unchecked Exception
-CAUSED_BY: JsonMappingException: Cannot invoke "java.util.Collection.iterator()" because "attributes" is null (through reference chain: org.openprovenance.prov.core.json.serialization.SortedDocument["entity"]-&gt;java.util.LinkedHashMap["e1"]-&gt;org.openprovenance.prov.vanilla.Entity["ex:missing"])
-CAUSED_BY: NullPointerException: Cannot invoke "java.util.Collection.iterator()" because "attributes" is null</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>WHAT WORKS: All other JSON value types as attribute values.
-WHAT BREAKS: JSON null as an attribute value crashes the parser with NullPointerException.</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Defensive error handling</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>VERIFIED: Remove or replace null attribute values before passing to ProvToolbox.
-Tested: replacing null with a valid value works fine.</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Should the parser handle null gracefully? JSON null is a valid JSON value — should it be ignored with a warning, or is crashing the intended behavior for invalid PROV-JSON input?</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>D3.3-1</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>3.3-01_minimal_bundle</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": { "ex": "http://example.org/" },
@@ -907,153 +762,153 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>PARSE_FAILED</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>EXCEPTION: UncheckedException: Unchecked Exception
 CAUSED_BY: JsonMappingException: Cannot invoke "org.openprovenance.prov.model.QualifiedName.getPrefix()" because "this.id" is null (through reference chain: org.openprovenance.prov.core.json.serialization.SortedDocument["bundle"]-&gt;java.util.HashMap["ex:bundle1"])
 CAUSED_BY: NullPointerException: Cannot invoke "org.openprovenance.prov.model.QualifiedName.getPrefix()" because "this.id" is null</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>WHAT WORKS: Top-level statements outside bundles.
 WHAT BREAKS: Every single bundle test crashes with NullPointerException. Bundles cannot be deserialized at all in PROV-JSON format.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Spec Section 3.3, Examples 40-41</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>VERIFIED: Extract bundle contents as separate standalone documents. Round-trip individually.
 Tested: extracted bundle content produces ROUND_TRIP_IDENTICAL.
 Alternative: Use PROV-N format for bundle-containing documents.</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Is PROV-JSON bundle support known to be broken? Is it a work-in-progress? The NPE is in SortedBundle.toBundle() where this.id is null — is the bundle ID supposed to be set during deserialization through a different mechanism?</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Data loss on valid native JSON values: ProvToolbox either drops them silently (D2.2-2) or crashes (D2.2-3). 17 of ~25 spec examples use native values — this affects the majority of the spec.</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Bundles completely non-functional (D3.3-1). Spec Section 3.3 (Examples 40-41) entirely broken.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Data loss on valid native JSON values: ProvToolbox either drops them silently (D2.2-2) or crashes (D2.2-3). 17 of ~25 spec examples use native values — this affects the majority of the spec.</t>
+          <t>WORKAROUNDS VERIFIED: Convert native values to typed format. Extract bundles as separate docs.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>prov:value content lost (D2.2-5). Null values crash (D2.2-6). Bundles completely non-functional (D3.3-1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>WORKAROUNDS VERIFIED: Convert native values to typed format. Rename prov:value to custom attribute. Extract bundles as separate docs.</t>
+          <t>KEY QUESTION: Are native values (MAY in spec) intentionally unsupported? 17 of ~25 spec examples would fail. Are bundles a known limitation?</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>KEY QUESTION: Are native values (MAY in spec) intentionally unsupported? 17 of ~25 spec examples would fail. Is prov:value @JsonIgnore intentional? Are bundles a known limitation?</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>HIGH ISSUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>HIGH ISSUES</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>D2.2-1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>2.2-01_spec_example1_typed</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1071,12 +926,12 @@
 </t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1093,49 +948,49 @@
 }</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Typed values are parsed correctly — the data survives.
 WHAT BREAKS: Single typed values output as 2-element arrays ["type","value"] instead of {"$":"value","type":"type"} objects. Multi-value attributes correctly use objects.
 CLEAR SPEC VIOLATION: Spec defines ONE format — {"$": value, "type": type}. The array format has zero basis in the spec.</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Spec Section 2.2, Example 1.
 Spec text: "The value of a literal is stored in the object's special property $... the data type in the type property."
 No alternative format defined anywhere in the spec.</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS OUTPUT: Convert 2-element arrays in attribute positions to {"$":value, "type":type} objects.
 Tested: data survives — both type and value are present in output.</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>Is the [type, value] array format a deliberate alternative? The spec defines only the {"$","type"} object format (Example 1). Is there documentation for this alternative? Other tools expect the spec format.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>D3.1.3-1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>3.1.3-01_spec_example9</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1156,12 +1011,12 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -1177,14 +1032,14 @@
 }</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>WHAT WORKS: Timestamps are parsed and date/time values preserved.
 WHAT BREAKS: Local timezone injected into timezone-unspecified timestamps. Milliseconds ".000" added.
 SEMANTIC CHANGE: In xsd:dateTime, "2011-11-16T16:05:00" (no timezone) and "2011-11-16T16:05:00.000+01:00" (with timezone) are DIFFERENT values. No timezone means "unspecified," not "local time." Injecting timezone changes the meaning of the data.</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Spec Section 3.1.3, Example 9: timestamps shown as "2011-11-16T16:05:00" (no timezone, no milliseconds).
 Spec: "values of startTime and endTime MUST conform to xsd:dateTime."
@@ -1192,102 +1047,250 @@
 In xsd:dateTime, absent timezone != UTC != local — they are semantically different.</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>POST-PROCESS: Store original timestamps before round-trip, restore after.
 Tested: timestamp data is present but modified. Also: the "ex:host" native string attribute is dropped (D2.2-2).</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>Injecting timezone changes the semantic meaning of the timestamp. Every spec example has no timezone. Is DateTimeOption.PRESERVE supposed to keep the original format? Is timezone injection configurable?</t>
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>CLEAR SPEC VIOLATION: Typed values output as [type, value] arrays instead of {"$","type"} objects (D2.2-1). Spec defines ONE format in Example 1.</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>HIGH — SUMMARY &amp; KEY QUESTIONS</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SEMANTIC CHANGE: Timezone injected into timestamps (D3.1.3-1). In xsd:dateTime, absent timezone != local time. Every spec example (9,11,13,17,21,41) has no timezone. Injecting one changes the meaning.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>CLEAR SPEC VIOLATION: Typed values output as [type, value] arrays instead of {"$","type"} objects (D2.2-1). Spec defines ONE format in Example 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>SEMANTIC CHANGE: Timezone injected into timestamps (D3.1.3-1). In xsd:dateTime, absent timezone != local time. Every spec example (9,11,13,17,21,41) has no timezone. Injecting one changes the meaning.</t>
+          <t>WORKAROUNDS: Post-process arrays to objects (D2.2-1). Store/restore original timestamps (D3.1.3-1).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>WORKAROUNDS: Post-process arrays to objects (D2.2-1). Store/restore original timestamps (D3.1.3-1).</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM ISSUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Input JSON</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Output / Error</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Problem Description</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Spec Reference</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Workaround (Verified)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Questions for Developer</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM ISSUES</t>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>D2.2-5</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>2.2-15_prov_value_typed</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "prefix": {
+    "default": "http://example.org/",
+    "ex": "http://example.org/"
+  },
+  "entity": {
+    "e1": {
+      "prov:value": {"$": "42", "type": "xsd:int"}
+    }
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>ROUND_TRIP_CHANGED</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>{
+"prefix" : {
+"default" : "http://example.org/",
+"ex" : "http://example.org/"
+},
+"entity" : {
+"e1" : {
+"prov:value" : [ "xsd:int" ]
+}
+}
+}</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: prov:value is parsed and stored internally. prov:type and prov:label serialize fine.
+WHAT BREAKS: prov:value is not written back out. The type name "xsd:int" survives but the actual value "42" is lost.
+NO SPEC BACKING: No PROV-JSON spec example uses prov:value. prov:type appears in 18+ examples and works fine. Both are standard PROV attributes — only prov:value has @JsonIgnore.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>No PROV-JSON spec example uses prov:value.
+prov:type (handled correctly) appears in Examples 5,7,9,11,15,17,19,25,27,29,31,37,41,42,43,45,47,51.
+prov:value is not demonstrated in the JSON spec.</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>VERIFIED: Rename "prov:value" to a custom attribute (e.g., "ex:provValue") before input. Rename back after output.
+Tested: data survives when using custom attribute name.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>No spec example uses prov:value. Is the @JsonIgnore intentional? prov:type and prov:label serialize fine — why is prov:value different?</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Issue ID</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Input JSON</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Output / Error</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Problem Description</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Spec Reference</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Workaround (Verified)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Questions for Developer</t>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>D2.2-6</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>2.2-21_json_null_value</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "prefix": {
+    "default": "http://example.org/",
+    "ex": "http://example.org/"
+  },
+  "entity": {
+    "e1": {
+      "ex:missing": null
+    }
+  }
+}
+</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>PARSE_FAILED</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>EXCEPTION: UncheckedException: Unchecked Exception
+CAUSED_BY: JsonMappingException: Cannot invoke "java.util.Collection.iterator()" because "attributes" is null (through reference chain: org.openprovenance.prov.core.json.serialization.SortedDocument["entity"]-&gt;java.util.LinkedHashMap["e1"]-&gt;org.openprovenance.prov.vanilla.Entity["ex:missing"])
+CAUSED_BY: NullPointerException: Cannot invoke "java.util.Collection.iterator()" because "attributes" is null</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>WHAT WORKS: All other JSON value types as attribute values.
+WHAT BREAKS: JSON null as an attribute value crashes the parser with NullPointerException.
+NO SPEC BACKING: No spec example uses null. Section 2.2 says native values MAY be "string, number, boolean" — null is not listed. Null is arguably not valid PROV-JSON. But crashing is still poor error handling.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>No spec example uses null.
+Spec Section 2.2 lists "string, number, boolean" as valid native types — null not included.
+Null is arguably invalid PROV-JSON input.</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>VERIFIED: Remove or replace null attribute values before passing to ProvToolbox.
+Tested: replacing null with a valid value works fine.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Null is not listed as valid PROV-JSON. But should invalid input crash or give a clean error message?</t>
         </is>
       </c>
     </row>
@@ -1885,100 +1888,107 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Side effects and optional extensions: D2.2-7 (inconsistency from D2.2-2), D2.2-8 (downstream of D2.2-1), D3.1.2-1 (prov:value — no spec example), D3.1.2-2 (xsd:string stripping — spec says MAY), D-DICT-1 (W3C Note, optional).</t>
+          <t>No spec backing: D2.2-5 (prov:value — no spec example uses it), D2.2-6 (null — not listed as valid PROV-JSON), D3.1.2-1 (prov:value on agents — same as D2.2-5).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Ordering not preserved in arrays and sections (D2.2-4, D3.1.1-4). HashSet/HashMap usage.</t>
+          <t>Side effects: D2.2-7 (inconsistency from D2.2-2), D2.2-8 (downstream of D2.2-1).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>KEY QUESTION: Are these intentional design choices or side effects of the CRITICAL/HIGH issues?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+          <t>Spec-permitted or optional: D3.1.2-2 (xsd:string stripping — spec says MAY), D-DICT-1 (W3C Note, optional extension).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Ordering: D2.2-4, D3.1.1-4 (HashSet/HashMap usage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>LOW ISSUES</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Issue ID</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Input JSON</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Output / Error</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Problem Description</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Spec Reference</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Workaround (Verified)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Questions for Developer</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>D2.1-7</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>2.1-12_user_underscore_prefix</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -1992,12 +2002,12 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2009,48 +2019,48 @@
 }</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: All other user-defined namespace prefixes.
 WHAT BREAKS: Using "_" as a namespace prefix — it gets silently overwritten by ProvToolbox's internal blank node mapping.
 Likely a design choice: Spec Section 2.1 reserves "_:" for blank node IDs (e.g. _:A1). ProvToolbox extends this by reserving the "_" prefix entirely. This is consistent with Turtle/RDF conventions.</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>Spec Section 2.1: "blank node identifiers MUST be created following the nodeID production in Turtle (e.g. _:A1)".
 No spec example uses "_" as a user-defined prefix. Reserving "_" is consistent with RDF blank node conventions.</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>VERIFIED: Rename "_" prefix to something else (e.g., "u").
 Tested: "u" prefix and "u:foo" entity survive correctly.</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>Likely a design choice. The spec reserves "_:" for blank nodes — is extending that to the entire "_" prefix intentional? Should there be a warning when a user tries to use "_" as a namespace prefix?</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-5</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>3.1.1-08_duplicate_entity_id</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2070,12 +2080,12 @@
 </t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2090,46 +2100,46 @@
 }</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: Standard documents without duplicate keys.
 WHAT BREAKS: Duplicate entity IDs — last wins.</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>RFC 8259</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>Accept — standard JSON parser behavior.
 Tested: last definition survives.</t>
         </is>
       </c>
-      <c r="J43" s="12" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>Standard JSON behavior. Could ProvToolbox detect and warn about duplicate keys during parsing? Or is silent last-wins the preferred approach?</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-7</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>3.1.1-20_prov_role</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2144,12 +2154,12 @@
 </t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2161,46 +2171,46 @@
 }</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: prov:role on relations.
 WHAT BREAKS: prov:role on elements (entities, agents) is dropped.</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>PROV-DM</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>VERIFIED: Rename "prov:role" to custom attribute on elements.
 Tested: "ex:role" survives on entities.</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>Is dropping prov:role on elements intentional? PROV-DM defines prov:role for relations, not elements — but should unknown prov: attributes be preserved as generic attributes rather than dropped?</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>D3.1.1-8</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>3.1.1-12_empty_entity_section</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2211,12 +2221,12 @@
 </t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2225,46 +2235,46 @@
 }</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: Non-empty sections always included.
 WHAT BREAKS: Empty sections dropped.</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>Spec examples</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>Accept — empty sections carry no data.
 Tested: section dropped, no data loss.</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>Is @JsonInclude(NON_EMPTY) intentional to keep output clean? Should empty sections be preserved for schema compliance?</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>D3.2.2-1</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>3.2.2-01_spec_example13</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">{
   "prefix": {
@@ -2288,12 +2298,12 @@
 </t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>ROUND_TRIP_CHANGED</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>{
 "prefix" : {
@@ -2314,71 +2324,72 @@
 }</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>WHAT WORKS: All relation data preserved.
 WHAT BREAKS: Property order within relation objects changes.</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>JSON specification</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>Accept — JSON key order not guaranteed.
 Tested: all properties and values intact.</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>Standard JSON behavior. Is there a @JsonPropertyOrder that could enforce consistent ordering if needed for interoperability testing?</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>LOW — SUMMARY &amp; KEY QUESTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Minor structural differences: property ordering, empty sections, duplicate keys, prov:role scope, underscore prefix. No data lost.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>D2.1-7 ("_" prefix): Spec reserves "_:" for blank nodes. ProvToolbox extending this to the prefix is consistent with RDF conventions.</t>
+          <t>Minor structural differences: property ordering, empty sections, duplicate keys, prov:role scope, underscore prefix. No data lost.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>D2.1-7 ("_" prefix): Spec reserves "_:" for blank nodes. ProvToolbox extending this to the prefix is consistent with RDF conventions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>KEY QUESTION: Are these design choices documented anywhere?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A23:J23"/>
+  <mergeCells count="14">
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
     <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
